--- a/research/traditional_assets/database/data/estonia/estonia_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_real_estate_development.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06929738574303698</v>
+        <v>0.06919479097155092</v>
       </c>
       <c r="C2">
-        <v>73.64342258503187</v>
+        <v>73.07481300513746</v>
       </c>
       <c r="D2">
-        <v>66.02342258503187</v>
+        <v>66.26181300513745</v>
       </c>
       <c r="E2">
-        <v>-63.99999999999999</v>
+        <v>-63.19299999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8069999999999999</v>
       </c>
       <c r="G2">
         <v>7.62</v>
@@ -1564,28 +1564,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04059209999999999</v>
       </c>
       <c r="N2">
-        <v>3.856666666666667</v>
+        <v>3.816074566666667</v>
       </c>
       <c r="O2">
-        <v>0.7713333333333334</v>
+        <v>0.7632149133333335</v>
       </c>
       <c r="P2">
-        <v>3.085333333333334</v>
+        <v>3.052859653333333</v>
       </c>
       <c r="Q2">
-        <v>3.145333333333334</v>
+        <v>3.112859653333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06929738574303698</v>
+        <v>0.06948726360762719</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241994</v>
+        <v>0.4493386376512636</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>95.01027704077069</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06919479097155092</v>
+        <v>0.06909219620006483</v>
       </c>
       <c r="C3">
-        <v>73.07481300513746</v>
+        <v>72.50793117365416</v>
       </c>
       <c r="D3">
-        <v>66.26181300513745</v>
+        <v>66.50193117365416</v>
       </c>
       <c r="E3">
-        <v>-63.19299999999999</v>
+        <v>-62.386</v>
       </c>
       <c r="F3">
-        <v>0.8069999999999999</v>
+        <v>1.614</v>
       </c>
       <c r="G3">
         <v>7.62</v>
@@ -1646,28 +1646,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M3">
-        <v>0.04059209999999999</v>
+        <v>0.08118419999999998</v>
       </c>
       <c r="N3">
-        <v>3.816074566666667</v>
+        <v>3.775482466666667</v>
       </c>
       <c r="O3">
-        <v>0.7632149133333335</v>
+        <v>0.7550964933333334</v>
       </c>
       <c r="P3">
-        <v>3.052859653333333</v>
+        <v>3.020385973333334</v>
       </c>
       <c r="Q3">
-        <v>3.112859653333333</v>
+        <v>3.080385973333334</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06948726360762719</v>
+        <v>0.0696810165306784</v>
       </c>
       <c r="T3">
-        <v>0.4493386376512636</v>
+        <v>0.4530140590054108</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>95.01027704077069</v>
+        <v>47.50513852038534</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06909219620006483</v>
+        <v>0.06898960142857877</v>
       </c>
       <c r="C4">
-        <v>72.50793117365416</v>
+        <v>71.94279594183007</v>
       </c>
       <c r="D4">
-        <v>66.50193117365416</v>
+        <v>66.74379594183007</v>
       </c>
       <c r="E4">
-        <v>-62.386</v>
+        <v>-61.57899999999999</v>
       </c>
       <c r="F4">
-        <v>1.614</v>
+        <v>2.420999999999999</v>
       </c>
       <c r="G4">
         <v>7.62</v>
@@ -1728,28 +1728,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M4">
-        <v>0.08118419999999998</v>
+        <v>0.1217763</v>
       </c>
       <c r="N4">
-        <v>3.775482466666667</v>
+        <v>3.734890366666667</v>
       </c>
       <c r="O4">
-        <v>0.7550964933333334</v>
+        <v>0.7469780733333334</v>
       </c>
       <c r="P4">
-        <v>3.020385973333334</v>
+        <v>2.987912293333333</v>
       </c>
       <c r="Q4">
-        <v>3.080385973333334</v>
+        <v>3.047912293333333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0696810165306784</v>
+        <v>0.06987876435935955</v>
       </c>
       <c r="T4">
-        <v>0.4530140590054108</v>
+        <v>0.4567652622431486</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.50513852038534</v>
+        <v>31.67009234692356</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06898960142857877</v>
+        <v>0.0688870066570927</v>
       </c>
       <c r="C5">
-        <v>71.94279594183007</v>
+        <v>71.37942643615925</v>
       </c>
       <c r="D5">
-        <v>66.74379594183007</v>
+        <v>66.98742643615924</v>
       </c>
       <c r="E5">
-        <v>-61.57899999999999</v>
+        <v>-60.77199999999999</v>
       </c>
       <c r="F5">
-        <v>2.420999999999999</v>
+        <v>3.228</v>
       </c>
       <c r="G5">
         <v>7.62</v>
@@ -1810,28 +1810,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M5">
-        <v>0.1217763</v>
+        <v>0.1623684</v>
       </c>
       <c r="N5">
-        <v>3.734890366666667</v>
+        <v>3.694298266666667</v>
       </c>
       <c r="O5">
-        <v>0.7469780733333334</v>
+        <v>0.7388596533333334</v>
       </c>
       <c r="P5">
-        <v>2.987912293333333</v>
+        <v>2.955438613333333</v>
       </c>
       <c r="Q5">
-        <v>3.047912293333333</v>
+        <v>3.015438613333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06987876435935955</v>
+        <v>0.07008063193447156</v>
       </c>
       <c r="T5">
-        <v>0.4567652622431486</v>
+        <v>0.4605946155483394</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.67009234692356</v>
+        <v>23.75256926019267</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0688870066570927</v>
+        <v>0.06878441188560661</v>
       </c>
       <c r="C6">
-        <v>71.37942643615925</v>
+        <v>70.81784206342365</v>
       </c>
       <c r="D6">
-        <v>66.98742643615924</v>
+        <v>67.23284206342365</v>
       </c>
       <c r="E6">
-        <v>-60.77199999999999</v>
+        <v>-59.965</v>
       </c>
       <c r="F6">
-        <v>3.228</v>
+        <v>4.034999999999999</v>
       </c>
       <c r="G6">
         <v>7.62</v>
@@ -1892,28 +1892,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M6">
-        <v>0.1623684</v>
+        <v>0.2029605</v>
       </c>
       <c r="N6">
-        <v>3.694298266666667</v>
+        <v>3.653706166666667</v>
       </c>
       <c r="O6">
-        <v>0.7388596533333334</v>
+        <v>0.7307412333333334</v>
       </c>
       <c r="P6">
-        <v>2.955438613333333</v>
+        <v>2.922964933333334</v>
       </c>
       <c r="Q6">
-        <v>3.015438613333334</v>
+        <v>2.982964933333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07008063193447156</v>
+        <v>0.07028674935327012</v>
       </c>
       <c r="T6">
-        <v>0.4605946155483394</v>
+        <v>0.4645045868178498</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.75256926019267</v>
+        <v>19.00205540815413</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06878441188560661</v>
+        <v>0.06868181711412055</v>
       </c>
       <c r="C7">
-        <v>70.81784206342365</v>
+        <v>70.25806251584608</v>
       </c>
       <c r="D7">
-        <v>67.23284206342365</v>
+        <v>67.48006251584607</v>
       </c>
       <c r="E7">
-        <v>-59.965</v>
+        <v>-59.15799999999999</v>
       </c>
       <c r="F7">
-        <v>4.034999999999999</v>
+        <v>4.842</v>
       </c>
       <c r="G7">
         <v>7.62</v>
@@ -1974,28 +1974,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M7">
-        <v>0.2029605</v>
+        <v>0.2435526</v>
       </c>
       <c r="N7">
-        <v>3.653706166666667</v>
+        <v>3.613114066666667</v>
       </c>
       <c r="O7">
-        <v>0.7307412333333334</v>
+        <v>0.7226228133333334</v>
       </c>
       <c r="P7">
-        <v>2.922964933333334</v>
+        <v>2.890491253333333</v>
       </c>
       <c r="Q7">
-        <v>2.982964933333334</v>
+        <v>2.950491253333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07028674935327012</v>
+        <v>0.07049725224906442</v>
       </c>
       <c r="T7">
-        <v>0.4645045868178498</v>
+        <v>0.4684977489654352</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.00205540815413</v>
+        <v>15.83504617346178</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06868181711412055</v>
+        <v>0.06857922234263447</v>
       </c>
       <c r="C8">
-        <v>70.25806251584608</v>
+        <v>69.700107776358</v>
       </c>
       <c r="D8">
-        <v>67.48006251584607</v>
+        <v>67.72910777635799</v>
       </c>
       <c r="E8">
-        <v>-59.15799999999999</v>
+        <v>-58.35099999999999</v>
       </c>
       <c r="F8">
-        <v>4.841999999999999</v>
+        <v>5.648999999999998</v>
       </c>
       <c r="G8">
         <v>7.62</v>
@@ -2056,28 +2056,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M8">
-        <v>0.2435525999999999</v>
+        <v>0.2841446999999999</v>
       </c>
       <c r="N8">
-        <v>3.613114066666667</v>
+        <v>3.572521966666667</v>
       </c>
       <c r="O8">
-        <v>0.7226228133333334</v>
+        <v>0.7145043933333334</v>
       </c>
       <c r="P8">
-        <v>2.890491253333333</v>
+        <v>2.858017573333334</v>
       </c>
       <c r="Q8">
-        <v>2.950491253333333</v>
+        <v>2.918017573333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07049725224906442</v>
+        <v>0.07071228208885427</v>
       </c>
       <c r="T8">
-        <v>0.4684977489654352</v>
+        <v>0.4725767855678071</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.83504617346178</v>
+        <v>13.5728967201101</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06857922234263446</v>
+        <v>0.0685726275711484</v>
       </c>
       <c r="C9">
-        <v>69.70010777635802</v>
+        <v>68.90917925088353</v>
       </c>
       <c r="D9">
-        <v>67.72910777635802</v>
+        <v>67.74517925088352</v>
       </c>
       <c r="E9">
-        <v>-58.35099999999999</v>
+        <v>-57.544</v>
       </c>
       <c r="F9">
-        <v>5.649</v>
+        <v>6.456</v>
       </c>
       <c r="G9">
         <v>7.62</v>
@@ -2138,45 +2138,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M9">
-        <v>0.2841447</v>
+        <v>0.3344208</v>
       </c>
       <c r="N9">
-        <v>3.572521966666667</v>
+        <v>3.522245866666667</v>
       </c>
       <c r="O9">
-        <v>0.7145043933333334</v>
+        <v>0.7044491733333335</v>
       </c>
       <c r="P9">
-        <v>2.858017573333334</v>
+        <v>2.817796693333334</v>
       </c>
       <c r="Q9">
-        <v>2.918017573333334</v>
+        <v>2.877796693333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07071228208885427</v>
+        <v>0.07093198649037868</v>
       </c>
       <c r="T9">
-        <v>0.4725767855678071</v>
+        <v>0.4767444968789263</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.5728967201101</v>
+        <v>11.53237677401246</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0685726275711484</v>
+        <v>0.06848203279966232</v>
       </c>
       <c r="C10">
-        <v>68.90917925088353</v>
+        <v>68.32373353407704</v>
       </c>
       <c r="D10">
-        <v>67.74517925088352</v>
+        <v>67.96673353407704</v>
       </c>
       <c r="E10">
-        <v>-57.544</v>
+        <v>-56.73699999999999</v>
       </c>
       <c r="F10">
-        <v>6.456</v>
+        <v>7.262999999999999</v>
       </c>
       <c r="G10">
         <v>7.62</v>
@@ -2220,28 +2220,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M10">
-        <v>0.3344208</v>
+        <v>0.3762233999999999</v>
       </c>
       <c r="N10">
-        <v>3.522245866666667</v>
+        <v>3.480443266666667</v>
       </c>
       <c r="O10">
-        <v>0.7044491733333335</v>
+        <v>0.6960886533333335</v>
       </c>
       <c r="P10">
-        <v>2.817796693333334</v>
+        <v>2.784354613333334</v>
       </c>
       <c r="Q10">
-        <v>2.877796693333334</v>
+        <v>2.844354613333334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07093198649037868</v>
+        <v>0.07115651956006848</v>
       </c>
       <c r="T10">
-        <v>0.4767444968789263</v>
+        <v>0.4810038062408393</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.53237677401246</v>
+        <v>10.25100157689997</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06848203279966232</v>
+        <v>0.06852743802817626</v>
       </c>
       <c r="C11">
-        <v>68.32373353407704</v>
+        <v>67.40551181160771</v>
       </c>
       <c r="D11">
-        <v>67.96673353407704</v>
+        <v>67.8555118116077</v>
       </c>
       <c r="E11">
-        <v>-56.73699999999999</v>
+        <v>-55.92999999999999</v>
       </c>
       <c r="F11">
-        <v>7.262999999999999</v>
+        <v>8.069999999999999</v>
       </c>
       <c r="G11">
         <v>7.62</v>
@@ -2302,45 +2302,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M11">
-        <v>0.3762233999999999</v>
+        <v>0.4317449999999999</v>
       </c>
       <c r="N11">
-        <v>3.480443266666667</v>
+        <v>3.424921666666667</v>
       </c>
       <c r="O11">
-        <v>0.6960886533333335</v>
+        <v>0.6849843333333334</v>
       </c>
       <c r="P11">
-        <v>2.784354613333334</v>
+        <v>2.739937333333334</v>
       </c>
       <c r="Q11">
-        <v>2.844354613333334</v>
+        <v>2.799937333333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07115651956006848</v>
+        <v>0.07138604225352917</v>
       </c>
       <c r="T11">
-        <v>0.4810038062408393</v>
+        <v>0.485357766921906</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.25100157689997</v>
+        <v>8.932741934861244</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06852743802817626</v>
+        <v>0.06845044325669018</v>
       </c>
       <c r="C12">
-        <v>67.40551181160771</v>
+        <v>66.78732856240282</v>
       </c>
       <c r="D12">
-        <v>67.8555118116077</v>
+        <v>68.04432856240281</v>
       </c>
       <c r="E12">
-        <v>-55.92999999999999</v>
+        <v>-55.12299999999999</v>
       </c>
       <c r="F12">
-        <v>8.069999999999999</v>
+        <v>8.876999999999999</v>
       </c>
       <c r="G12">
         <v>7.62</v>
@@ -2384,28 +2384,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M12">
-        <v>0.4317449999999999</v>
+        <v>0.4749194999999999</v>
       </c>
       <c r="N12">
-        <v>3.424921666666667</v>
+        <v>3.381747166666667</v>
       </c>
       <c r="O12">
-        <v>0.6849843333333334</v>
+        <v>0.6763494333333334</v>
       </c>
       <c r="P12">
-        <v>2.739937333333334</v>
+        <v>2.705397733333334</v>
       </c>
       <c r="Q12">
-        <v>2.799937333333334</v>
+        <v>2.765397733333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07138604225352917</v>
+        <v>0.07162072276032604</v>
       </c>
       <c r="T12">
-        <v>0.4853577669219061</v>
+        <v>0.4898095694160303</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.932741934861244</v>
+        <v>8.120674486237494</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06845044325669018</v>
+        <v>0.0684502484852041</v>
       </c>
       <c r="C13">
-        <v>66.78732856240282</v>
+        <v>65.9808075392521</v>
       </c>
       <c r="D13">
-        <v>68.04432856240281</v>
+        <v>68.04480753925209</v>
       </c>
       <c r="E13">
-        <v>-55.12299999999999</v>
+        <v>-54.316</v>
       </c>
       <c r="F13">
-        <v>8.876999999999999</v>
+        <v>9.683999999999997</v>
       </c>
       <c r="G13">
         <v>7.62</v>
@@ -2466,45 +2466,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M13">
-        <v>0.4749194999999999</v>
+        <v>0.5258411999999999</v>
       </c>
       <c r="N13">
-        <v>3.381747166666667</v>
+        <v>3.330825466666667</v>
       </c>
       <c r="O13">
-        <v>0.6763494333333334</v>
+        <v>0.6661650933333334</v>
       </c>
       <c r="P13">
-        <v>2.705397733333334</v>
+        <v>2.664660373333334</v>
       </c>
       <c r="Q13">
-        <v>2.765397733333334</v>
+        <v>2.724660373333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07162072276032604</v>
+        <v>0.07186073691500466</v>
       </c>
       <c r="T13">
-        <v>0.4898095694160303</v>
+        <v>0.4943625492395666</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.120674486237494</v>
+        <v>7.334280133748873</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0684502484852041</v>
+        <v>0.06837965371371803</v>
       </c>
       <c r="C14">
-        <v>65.9808075392521</v>
+        <v>65.34785760481643</v>
       </c>
       <c r="D14">
-        <v>68.04480753925209</v>
+        <v>68.21885760481642</v>
       </c>
       <c r="E14">
-        <v>-54.316</v>
+        <v>-53.50899999999999</v>
       </c>
       <c r="F14">
-        <v>9.683999999999997</v>
+        <v>10.491</v>
       </c>
       <c r="G14">
         <v>7.62</v>
@@ -2548,28 +2548,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M14">
-        <v>0.5258411999999999</v>
+        <v>0.5696613</v>
       </c>
       <c r="N14">
-        <v>3.330825466666667</v>
+        <v>3.287005366666667</v>
       </c>
       <c r="O14">
-        <v>0.6661650933333334</v>
+        <v>0.6574010733333334</v>
       </c>
       <c r="P14">
-        <v>2.664660373333334</v>
+        <v>2.629604293333334</v>
       </c>
       <c r="Q14">
-        <v>2.724660373333334</v>
+        <v>2.689604293333334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07186073691500466</v>
+        <v>0.0721062686364575</v>
       </c>
       <c r="T14">
-        <v>0.4943625492395666</v>
+        <v>0.4990201952659428</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.334280133748873</v>
+        <v>6.770104738845111</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06837965371371803</v>
+        <v>0.06830905894223196</v>
       </c>
       <c r="C15">
-        <v>65.34785760481643</v>
+        <v>64.71580035012825</v>
       </c>
       <c r="D15">
-        <v>68.21885760481642</v>
+        <v>68.39380035012825</v>
       </c>
       <c r="E15">
-        <v>-53.50899999999999</v>
+        <v>-52.70199999999999</v>
       </c>
       <c r="F15">
-        <v>10.491</v>
+        <v>11.298</v>
       </c>
       <c r="G15">
         <v>7.62</v>
@@ -2630,28 +2630,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M15">
-        <v>0.5696613</v>
+        <v>0.6134814000000001</v>
       </c>
       <c r="N15">
-        <v>3.287005366666667</v>
+        <v>3.243185266666667</v>
       </c>
       <c r="O15">
-        <v>0.6574010733333334</v>
+        <v>0.6486370533333334</v>
       </c>
       <c r="P15">
-        <v>2.629604293333334</v>
+        <v>2.594548213333334</v>
       </c>
       <c r="Q15">
-        <v>2.689604293333334</v>
+        <v>2.654548213333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0721062686364575</v>
+        <v>0.07235751039794414</v>
       </c>
       <c r="T15">
-        <v>0.4990201952659428</v>
+        <v>0.5037861586417696</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.770104738845111</v>
+        <v>6.286525828927603</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06830905894223196</v>
+        <v>0.06835846417074588</v>
       </c>
       <c r="C16">
-        <v>64.71580035012825</v>
+        <v>63.78627389265981</v>
       </c>
       <c r="D16">
-        <v>68.39380035012825</v>
+        <v>68.27127389265981</v>
       </c>
       <c r="E16">
-        <v>-52.70199999999999</v>
+        <v>-51.895</v>
       </c>
       <c r="F16">
-        <v>11.298</v>
+        <v>12.105</v>
       </c>
       <c r="G16">
         <v>7.62</v>
@@ -2712,45 +2712,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M16">
-        <v>0.6134814000000001</v>
+        <v>0.6694065</v>
       </c>
       <c r="N16">
-        <v>3.243185266666667</v>
+        <v>3.187260166666667</v>
       </c>
       <c r="O16">
-        <v>0.6486370533333334</v>
+        <v>0.6374520333333334</v>
       </c>
       <c r="P16">
-        <v>2.594548213333334</v>
+        <v>2.549808133333333</v>
       </c>
       <c r="Q16">
-        <v>2.654548213333334</v>
+        <v>2.609808133333333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07235751039794414</v>
+        <v>0.07261466373028927</v>
       </c>
       <c r="T16">
-        <v>0.5037861586417696</v>
+        <v>0.5086642623323216</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.286525828927603</v>
+        <v>5.761322405245044</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06835846417074588</v>
+        <v>0.0682958693992598</v>
       </c>
       <c r="C17">
-        <v>63.78627389265981</v>
+        <v>63.13458522820255</v>
       </c>
       <c r="D17">
-        <v>68.27127389265981</v>
+        <v>68.42658522820254</v>
       </c>
       <c r="E17">
-        <v>-51.895</v>
+        <v>-51.08799999999999</v>
       </c>
       <c r="F17">
-        <v>12.105</v>
+        <v>12.912</v>
       </c>
       <c r="G17">
         <v>7.62</v>
@@ -2794,28 +2794,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M17">
-        <v>0.6694064999999999</v>
+        <v>0.7140335999999999</v>
       </c>
       <c r="N17">
-        <v>3.187260166666667</v>
+        <v>3.142633066666667</v>
       </c>
       <c r="O17">
-        <v>0.6374520333333334</v>
+        <v>0.6285266133333334</v>
       </c>
       <c r="P17">
-        <v>2.549808133333333</v>
+        <v>2.514106453333333</v>
       </c>
       <c r="Q17">
-        <v>2.609808133333333</v>
+        <v>2.574106453333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07261466373028927</v>
+        <v>0.07287793976102357</v>
       </c>
       <c r="T17">
-        <v>0.5086642623323216</v>
+        <v>0.5136585113488392</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.761322405245045</v>
+        <v>5.40123975491723</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0682958693992598</v>
+        <v>0.06823327462777373</v>
       </c>
       <c r="C18">
-        <v>63.13458522820255</v>
+        <v>62.4836048150873</v>
       </c>
       <c r="D18">
-        <v>68.42658522820254</v>
+        <v>68.58260481508729</v>
       </c>
       <c r="E18">
-        <v>-51.08799999999999</v>
+        <v>-50.28099999999999</v>
       </c>
       <c r="F18">
-        <v>12.912</v>
+        <v>13.719</v>
       </c>
       <c r="G18">
         <v>7.62</v>
@@ -2876,28 +2876,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M18">
-        <v>0.7140335999999999</v>
+        <v>0.7586607</v>
       </c>
       <c r="N18">
-        <v>3.142633066666667</v>
+        <v>3.098005966666667</v>
       </c>
       <c r="O18">
-        <v>0.6285266133333334</v>
+        <v>0.6196011933333334</v>
       </c>
       <c r="P18">
-        <v>2.514106453333333</v>
+        <v>2.478404773333334</v>
       </c>
       <c r="Q18">
-        <v>2.574106453333334</v>
+        <v>2.538404773333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07287793976102357</v>
+        <v>0.07314755979249847</v>
       </c>
       <c r="T18">
-        <v>0.5136585113488392</v>
+        <v>0.5187731037151525</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.40123975491723</v>
+        <v>5.083519769333863</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06823327462777373</v>
+        <v>0.06817067985628765</v>
       </c>
       <c r="C19">
-        <v>62.4836048150873</v>
+        <v>61.83333750904137</v>
       </c>
       <c r="D19">
-        <v>68.58260481508729</v>
+        <v>68.73933750904136</v>
       </c>
       <c r="E19">
-        <v>-50.28099999999999</v>
+        <v>-49.47399999999999</v>
       </c>
       <c r="F19">
-        <v>13.719</v>
+        <v>14.526</v>
       </c>
       <c r="G19">
         <v>7.62</v>
@@ -2958,28 +2958,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M19">
-        <v>0.7586607</v>
+        <v>0.8032878</v>
       </c>
       <c r="N19">
-        <v>3.098005966666667</v>
+        <v>3.053378866666667</v>
       </c>
       <c r="O19">
-        <v>0.6196011933333334</v>
+        <v>0.6106757733333334</v>
       </c>
       <c r="P19">
-        <v>2.478404773333334</v>
+        <v>2.442703093333333</v>
       </c>
       <c r="Q19">
-        <v>2.538404773333334</v>
+        <v>2.502703093333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07314755979249847</v>
+        <v>0.07342375592230202</v>
       </c>
       <c r="T19">
-        <v>0.5187731037151525</v>
+        <v>0.5240124422367418</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.083519769333863</v>
+        <v>4.80110200437087</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06817067985628766</v>
+        <v>0.06810808508480158</v>
       </c>
       <c r="C20">
-        <v>61.83333750904134</v>
+        <v>61.18378821028104</v>
       </c>
       <c r="D20">
-        <v>68.73933750904133</v>
+        <v>68.89678821028103</v>
       </c>
       <c r="E20">
-        <v>-49.474</v>
+        <v>-48.66699999999999</v>
       </c>
       <c r="F20">
-        <v>14.526</v>
+        <v>15.333</v>
       </c>
       <c r="G20">
         <v>7.62</v>
@@ -3040,28 +3040,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M20">
-        <v>0.8032877999999999</v>
+        <v>0.8479148999999999</v>
       </c>
       <c r="N20">
-        <v>3.053378866666667</v>
+        <v>3.008751766666667</v>
       </c>
       <c r="O20">
-        <v>0.6106757733333334</v>
+        <v>0.6017503533333335</v>
       </c>
       <c r="P20">
-        <v>2.442703093333333</v>
+        <v>2.407001413333334</v>
       </c>
       <c r="Q20">
-        <v>2.502703093333333</v>
+        <v>2.467001413333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07342375592230202</v>
+        <v>0.07370677170963158</v>
       </c>
       <c r="T20">
-        <v>0.5240124422367417</v>
+        <v>0.5293811471415801</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.801102004370871</v>
+        <v>4.548412425193456</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06810808508480158</v>
+        <v>0.06844549031331551</v>
       </c>
       <c r="C21">
-        <v>61.18378821028104</v>
+        <v>59.53651080369512</v>
       </c>
       <c r="D21">
-        <v>68.89678821028103</v>
+        <v>68.05651080369512</v>
       </c>
       <c r="E21">
-        <v>-48.66699999999999</v>
+        <v>-47.86</v>
       </c>
       <c r="F21">
-        <v>15.333</v>
+        <v>16.14</v>
       </c>
       <c r="G21">
         <v>7.62</v>
@@ -3122,45 +3122,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M21">
-        <v>0.8479148999999999</v>
+        <v>0.9328919999999999</v>
       </c>
       <c r="N21">
-        <v>3.008751766666667</v>
+        <v>2.923774666666667</v>
       </c>
       <c r="O21">
-        <v>0.6017503533333335</v>
+        <v>0.5847549333333334</v>
       </c>
       <c r="P21">
-        <v>2.407001413333334</v>
+        <v>2.339019733333334</v>
       </c>
       <c r="Q21">
-        <v>2.467001413333334</v>
+        <v>2.399019733333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07370677170963158</v>
+        <v>0.07399686289164438</v>
       </c>
       <c r="T21">
-        <v>0.5293811471415801</v>
+        <v>0.5348840696690392</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.548412425193456</v>
+        <v>4.134097694767098</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06844549031331551</v>
+        <v>0.06899089554182944</v>
       </c>
       <c r="C22">
-        <v>59.53651080369512</v>
+        <v>57.41373414486378</v>
       </c>
       <c r="D22">
-        <v>68.05651080369512</v>
+        <v>66.74073414486378</v>
       </c>
       <c r="E22">
-        <v>-47.86</v>
+        <v>-47.053</v>
       </c>
       <c r="F22">
-        <v>16.14</v>
+        <v>16.947</v>
       </c>
       <c r="G22">
         <v>7.62</v>
@@ -3204,45 +3204,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M22">
-        <v>0.9328919999999999</v>
+        <v>1.0388511</v>
       </c>
       <c r="N22">
-        <v>2.923774666666667</v>
+        <v>2.817815566666667</v>
       </c>
       <c r="O22">
-        <v>0.5847549333333334</v>
+        <v>0.5635631133333334</v>
       </c>
       <c r="P22">
-        <v>2.339019733333334</v>
+        <v>2.254252453333334</v>
       </c>
       <c r="Q22">
-        <v>2.399019733333334</v>
+        <v>2.314252453333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07399686289164438</v>
+        <v>0.07429429815421447</v>
       </c>
       <c r="T22">
-        <v>0.5348840696690392</v>
+        <v>0.5405263066908645</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.134097694767098</v>
+        <v>3.712434502564099</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06899089554182944</v>
+        <v>0.06897630077034336</v>
       </c>
       <c r="C23">
-        <v>57.41373414486379</v>
+        <v>56.64128081746227</v>
       </c>
       <c r="D23">
-        <v>66.74073414486378</v>
+        <v>66.77528081746226</v>
       </c>
       <c r="E23">
-        <v>-47.053</v>
+        <v>-46.246</v>
       </c>
       <c r="F23">
-        <v>16.947</v>
+        <v>17.754</v>
       </c>
       <c r="G23">
         <v>7.62</v>
@@ -3286,28 +3286,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M23">
-        <v>1.0388511</v>
+        <v>1.0883202</v>
       </c>
       <c r="N23">
-        <v>2.817815566666667</v>
+        <v>2.768346466666667</v>
       </c>
       <c r="O23">
-        <v>0.5635631133333334</v>
+        <v>0.5536692933333335</v>
       </c>
       <c r="P23">
-        <v>2.254252453333334</v>
+        <v>2.214677173333334</v>
       </c>
       <c r="Q23">
-        <v>2.314252453333334</v>
+        <v>2.274677173333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07429429815421447</v>
+        <v>0.07459935996197867</v>
       </c>
       <c r="T23">
-        <v>0.5405263066908645</v>
+        <v>0.5463132164568393</v>
       </c>
       <c r="U23">
         <v>0.0613</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.712434502564099</v>
+        <v>3.543687479720277</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06897630077034336</v>
+        <v>0.06947690599885729</v>
       </c>
       <c r="C24">
-        <v>56.64128081746227</v>
+        <v>54.66938809255907</v>
       </c>
       <c r="D24">
-        <v>66.77528081746226</v>
+        <v>65.61038809255906</v>
       </c>
       <c r="E24">
-        <v>-46.246</v>
+        <v>-45.43899999999999</v>
       </c>
       <c r="F24">
-        <v>17.754</v>
+        <v>18.561</v>
       </c>
       <c r="G24">
         <v>7.62</v>
@@ -3368,45 +3368,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M24">
-        <v>1.0883202</v>
+        <v>1.1897601</v>
       </c>
       <c r="N24">
-        <v>2.768346466666667</v>
+        <v>2.666906566666667</v>
       </c>
       <c r="O24">
-        <v>0.5536692933333335</v>
+        <v>0.5333813133333334</v>
       </c>
       <c r="P24">
-        <v>2.214677173333334</v>
+        <v>2.133525253333334</v>
       </c>
       <c r="Q24">
-        <v>2.274677173333334</v>
+        <v>2.193525253333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07459935996197867</v>
+        <v>0.07491234545306141</v>
       </c>
       <c r="T24">
-        <v>0.5463132164568393</v>
+        <v>0.5522504355673847</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.543687479720277</v>
+        <v>3.241549844096022</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06947690599885729</v>
+        <v>0.06948471122737121</v>
       </c>
       <c r="C25">
-        <v>54.66938809255907</v>
+        <v>53.84454726695267</v>
       </c>
       <c r="D25">
-        <v>65.61038809255906</v>
+        <v>65.59254726695266</v>
       </c>
       <c r="E25">
-        <v>-45.43899999999999</v>
+        <v>-44.63199999999999</v>
       </c>
       <c r="F25">
-        <v>18.561</v>
+        <v>19.368</v>
       </c>
       <c r="G25">
         <v>7.62</v>
@@ -3450,28 +3450,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M25">
-        <v>1.1897601</v>
+        <v>1.2414888</v>
       </c>
       <c r="N25">
-        <v>2.666906566666667</v>
+        <v>2.615177866666667</v>
       </c>
       <c r="O25">
-        <v>0.5333813133333334</v>
+        <v>0.5230355733333334</v>
       </c>
       <c r="P25">
-        <v>2.133525253333334</v>
+        <v>2.092142293333334</v>
       </c>
       <c r="Q25">
-        <v>2.193525253333334</v>
+        <v>2.152142293333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07491234545306141</v>
+        <v>0.07523356740443581</v>
       </c>
       <c r="T25">
-        <v>0.5522504355673847</v>
+        <v>0.5583438972861025</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.241549844096022</v>
+        <v>3.106485267258687</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06948471122737121</v>
+        <v>0.07105251645588515</v>
       </c>
       <c r="C26">
-        <v>53.84454726695267</v>
+        <v>49.64045400633202</v>
       </c>
       <c r="D26">
-        <v>65.59254726695266</v>
+        <v>62.19545400633202</v>
       </c>
       <c r="E26">
-        <v>-44.632</v>
+        <v>-43.825</v>
       </c>
       <c r="F26">
-        <v>19.36799999999999</v>
+        <v>20.175</v>
       </c>
       <c r="G26">
         <v>7.62</v>
@@ -3532,45 +3532,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M26">
-        <v>1.2414888</v>
+        <v>1.4505825</v>
       </c>
       <c r="N26">
-        <v>2.615177866666667</v>
+        <v>2.406084166666667</v>
       </c>
       <c r="O26">
-        <v>0.5230355733333335</v>
+        <v>0.4812168333333334</v>
       </c>
       <c r="P26">
-        <v>2.092142293333334</v>
+        <v>1.924867333333334</v>
       </c>
       <c r="Q26">
-        <v>2.152142293333334</v>
+        <v>1.984867333333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07523356740443581</v>
+        <v>0.07556335527451352</v>
       </c>
       <c r="T26">
-        <v>0.5583438972861023</v>
+        <v>0.5645998513173192</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.106485267258688</v>
+        <v>2.658702050153416</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07105251645588515</v>
+        <v>0.07112272168439907</v>
       </c>
       <c r="C27">
-        <v>49.64045400633202</v>
+        <v>48.68954667065336</v>
       </c>
       <c r="D27">
-        <v>62.19545400633202</v>
+        <v>62.05154667065335</v>
       </c>
       <c r="E27">
-        <v>-43.825</v>
+        <v>-43.01799999999999</v>
       </c>
       <c r="F27">
-        <v>20.175</v>
+        <v>20.982</v>
       </c>
       <c r="G27">
         <v>7.62</v>
@@ -3614,28 +3614,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M27">
-        <v>1.4505825</v>
+        <v>1.5086058</v>
       </c>
       <c r="N27">
-        <v>2.406084166666667</v>
+        <v>2.348060866666667</v>
       </c>
       <c r="O27">
-        <v>0.4812168333333334</v>
+        <v>0.4696121733333334</v>
       </c>
       <c r="P27">
-        <v>1.924867333333334</v>
+        <v>1.878448693333333</v>
       </c>
       <c r="Q27">
-        <v>1.984867333333334</v>
+        <v>1.938448693333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07556335527451352</v>
+        <v>0.075902056330269</v>
       </c>
       <c r="T27">
-        <v>0.5645998513173192</v>
+        <v>0.5710248851872176</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.658702050153416</v>
+        <v>2.556444278993669</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07112272168439907</v>
+        <v>0.07203532691291299</v>
       </c>
       <c r="C28">
-        <v>48.68954667065336</v>
+        <v>46.07070346813111</v>
       </c>
       <c r="D28">
-        <v>62.05154667065335</v>
+        <v>60.23970346813112</v>
       </c>
       <c r="E28">
-        <v>-43.01799999999999</v>
+        <v>-42.211</v>
       </c>
       <c r="F28">
-        <v>20.982</v>
+        <v>21.789</v>
       </c>
       <c r="G28">
         <v>7.62</v>
@@ -3696,45 +3696,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M28">
-        <v>1.5086058</v>
+        <v>1.6516062</v>
       </c>
       <c r="N28">
-        <v>2.348060866666667</v>
+        <v>2.205060466666667</v>
       </c>
       <c r="O28">
-        <v>0.4696121733333334</v>
+        <v>0.4410120933333334</v>
       </c>
       <c r="P28">
-        <v>1.878448693333333</v>
+        <v>1.764048373333333</v>
       </c>
       <c r="Q28">
-        <v>1.938448693333333</v>
+        <v>1.824048373333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.075902056330269</v>
+        <v>0.0762500368670041</v>
       </c>
       <c r="T28">
-        <v>0.5710248851872176</v>
+        <v>0.5776259473823188</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.556444278993669</v>
+        <v>2.335100623058127</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07203532691291299</v>
+        <v>0.07213673214142692</v>
       </c>
       <c r="C29">
-        <v>46.07070346813111</v>
+        <v>45.06888889510617</v>
       </c>
       <c r="D29">
-        <v>60.23970346813112</v>
+        <v>60.04488889510618</v>
       </c>
       <c r="E29">
-        <v>-42.211</v>
+        <v>-41.404</v>
       </c>
       <c r="F29">
-        <v>21.789</v>
+        <v>22.596</v>
       </c>
       <c r="G29">
         <v>7.62</v>
@@ -3778,28 +3778,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M29">
-        <v>1.6516062</v>
+        <v>1.7127768</v>
       </c>
       <c r="N29">
-        <v>2.205060466666667</v>
+        <v>2.143889866666667</v>
       </c>
       <c r="O29">
-        <v>0.4410120933333334</v>
+        <v>0.4287779733333335</v>
       </c>
       <c r="P29">
-        <v>1.764048373333333</v>
+        <v>1.715111893333334</v>
       </c>
       <c r="Q29">
-        <v>1.824048373333333</v>
+        <v>1.775111893333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0762500368670041</v>
+        <v>0.07660768352975961</v>
       </c>
       <c r="T29">
-        <v>0.5776259473823188</v>
+        <v>0.5844103724161726</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.335100623058127</v>
+        <v>2.251704172234623</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07213673214142692</v>
+        <v>0.07223813736994085</v>
       </c>
       <c r="C30">
-        <v>45.06888889510617</v>
+        <v>44.06833031680387</v>
       </c>
       <c r="D30">
-        <v>60.04488889510618</v>
+        <v>59.85133031680387</v>
       </c>
       <c r="E30">
-        <v>-41.404</v>
+        <v>-40.59699999999999</v>
       </c>
       <c r="F30">
-        <v>22.596</v>
+        <v>23.403</v>
       </c>
       <c r="G30">
         <v>7.62</v>
@@ -3860,28 +3860,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M30">
-        <v>1.7127768</v>
+        <v>1.7739474</v>
       </c>
       <c r="N30">
-        <v>2.143889866666667</v>
+        <v>2.082719266666667</v>
       </c>
       <c r="O30">
-        <v>0.4287779733333335</v>
+        <v>0.4165438533333334</v>
       </c>
       <c r="P30">
-        <v>1.715111893333334</v>
+        <v>1.666175413333334</v>
       </c>
       <c r="Q30">
-        <v>1.775111893333334</v>
+        <v>1.726175413333334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07660768352975961</v>
+        <v>0.07697540474639555</v>
       </c>
       <c r="T30">
-        <v>0.5844103724161726</v>
+        <v>0.5913859080143603</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.251704172234623</v>
+        <v>2.174059200778257</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07223813736994084</v>
+        <v>0.07233954259845476</v>
       </c>
       <c r="C31">
-        <v>44.06833031680391</v>
+        <v>43.0690156259126</v>
       </c>
       <c r="D31">
-        <v>59.8513303168039</v>
+        <v>59.65901562591259</v>
       </c>
       <c r="E31">
-        <v>-40.59699999999999</v>
+        <v>-39.78999999999999</v>
       </c>
       <c r="F31">
-        <v>23.403</v>
+        <v>24.21</v>
       </c>
       <c r="G31">
         <v>7.62</v>
@@ -3942,28 +3942,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M31">
-        <v>1.7739474</v>
+        <v>1.835118</v>
       </c>
       <c r="N31">
-        <v>2.082719266666667</v>
+        <v>2.021548666666667</v>
       </c>
       <c r="O31">
-        <v>0.4165438533333335</v>
+        <v>0.4043097333333334</v>
       </c>
       <c r="P31">
-        <v>1.666175413333334</v>
+        <v>1.617238933333333</v>
       </c>
       <c r="Q31">
-        <v>1.726175413333334</v>
+        <v>1.677238933333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07697540474639555</v>
+        <v>0.07735363228350681</v>
       </c>
       <c r="T31">
-        <v>0.5913859080143603</v>
+        <v>0.5985607446296393</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.174059200778257</v>
+        <v>2.101590560752315</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07233954259845476</v>
+        <v>0.07244094782696869</v>
       </c>
       <c r="C32">
-        <v>43.0690156259126</v>
+        <v>42.07093287023532</v>
       </c>
       <c r="D32">
-        <v>59.65901562591259</v>
+        <v>59.46793287023532</v>
       </c>
       <c r="E32">
-        <v>-39.78999999999999</v>
+        <v>-38.983</v>
       </c>
       <c r="F32">
-        <v>24.21</v>
+        <v>25.017</v>
       </c>
       <c r="G32">
         <v>7.62</v>
@@ -4024,28 +4024,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M32">
-        <v>1.835118</v>
+        <v>1.8962886</v>
       </c>
       <c r="N32">
-        <v>2.021548666666667</v>
+        <v>1.960378066666667</v>
       </c>
       <c r="O32">
-        <v>0.4043097333333334</v>
+        <v>0.3920756133333334</v>
       </c>
       <c r="P32">
-        <v>1.617238933333333</v>
+        <v>1.568302453333334</v>
       </c>
       <c r="Q32">
-        <v>1.677238933333334</v>
+        <v>1.628302453333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07735363228350681</v>
+        <v>0.07774282293763579</v>
       </c>
       <c r="T32">
-        <v>0.5985607446296393</v>
+        <v>0.6059435475236218</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.101590560752315</v>
+        <v>2.033797316857079</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07244094782696869</v>
+        <v>0.07617755305548261</v>
       </c>
       <c r="C33">
-        <v>42.07093287023532</v>
+        <v>34.98631541309052</v>
       </c>
       <c r="D33">
-        <v>59.46793287023532</v>
+        <v>53.19031541309052</v>
       </c>
       <c r="E33">
-        <v>-38.983</v>
+        <v>-38.17599999999999</v>
       </c>
       <c r="F33">
-        <v>25.017</v>
+        <v>25.824</v>
       </c>
       <c r="G33">
         <v>7.62</v>
@@ -4106,45 +4106,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M33">
-        <v>1.8962886</v>
+        <v>2.32416</v>
       </c>
       <c r="N33">
-        <v>1.960378066666667</v>
+        <v>1.532506666666667</v>
       </c>
       <c r="O33">
-        <v>0.3920756133333334</v>
+        <v>0.3065013333333335</v>
       </c>
       <c r="P33">
-        <v>1.568302453333334</v>
+        <v>1.226005333333334</v>
       </c>
       <c r="Q33">
-        <v>1.628302453333334</v>
+        <v>1.286005333333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07774282293763579</v>
+        <v>0.07814346037570974</v>
       </c>
       <c r="T33">
-        <v>0.6059435475236218</v>
+        <v>0.6135434916791921</v>
       </c>
       <c r="U33">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.033797316857079</v>
+        <v>1.659380880260682</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07617755305548261</v>
+        <v>0.07639255828399655</v>
       </c>
       <c r="C34">
-        <v>34.98631541309052</v>
+        <v>33.85818133502367</v>
       </c>
       <c r="D34">
-        <v>53.19031541309052</v>
+        <v>52.86918133502367</v>
       </c>
       <c r="E34">
-        <v>-38.17599999999999</v>
+        <v>-37.369</v>
       </c>
       <c r="F34">
-        <v>25.824</v>
+        <v>26.631</v>
       </c>
       <c r="G34">
         <v>7.62</v>
@@ -4188,28 +4188,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M34">
-        <v>2.32416</v>
+        <v>2.39679</v>
       </c>
       <c r="N34">
-        <v>1.532506666666667</v>
+        <v>1.459876666666667</v>
       </c>
       <c r="O34">
-        <v>0.3065013333333335</v>
+        <v>0.2919753333333334</v>
       </c>
       <c r="P34">
-        <v>1.226005333333334</v>
+        <v>1.167901333333334</v>
       </c>
       <c r="Q34">
-        <v>1.286005333333334</v>
+        <v>1.227901333333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07814346037570974</v>
+        <v>0.07855605714029336</v>
       </c>
       <c r="T34">
-        <v>0.6135434916791921</v>
+        <v>0.6213702998394064</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.659380880260682</v>
+        <v>1.609096611161874</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07639255828399655</v>
+        <v>0.07660756351251047</v>
       </c>
       <c r="C35">
-        <v>33.85818133502367</v>
+        <v>32.73390165062685</v>
       </c>
       <c r="D35">
-        <v>52.86918133502367</v>
+        <v>52.55190165062685</v>
       </c>
       <c r="E35">
-        <v>-37.369</v>
+        <v>-36.562</v>
       </c>
       <c r="F35">
-        <v>26.631</v>
+        <v>27.438</v>
       </c>
       <c r="G35">
         <v>7.62</v>
@@ -4270,28 +4270,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M35">
-        <v>2.39679</v>
+        <v>2.46942</v>
       </c>
       <c r="N35">
-        <v>1.459876666666667</v>
+        <v>1.387246666666667</v>
       </c>
       <c r="O35">
-        <v>0.2919753333333334</v>
+        <v>0.2774493333333334</v>
       </c>
       <c r="P35">
-        <v>1.167901333333334</v>
+        <v>1.109797333333334</v>
       </c>
       <c r="Q35">
-        <v>1.227901333333334</v>
+        <v>1.169797333333334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07855605714029336</v>
+        <v>0.07898115683713708</v>
       </c>
       <c r="T35">
-        <v>0.6213702998394064</v>
+        <v>0.6294342840044755</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.609096611161874</v>
+        <v>1.561770240245348</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07660756351251047</v>
+        <v>0.07682256874102439</v>
       </c>
       <c r="C36">
-        <v>32.73390165062685</v>
+        <v>31.61340738064572</v>
       </c>
       <c r="D36">
-        <v>52.55190165062685</v>
+        <v>52.23840738064572</v>
       </c>
       <c r="E36">
-        <v>-36.562</v>
+        <v>-35.755</v>
       </c>
       <c r="F36">
-        <v>27.438</v>
+        <v>28.245</v>
       </c>
       <c r="G36">
         <v>7.62</v>
@@ -4352,28 +4352,28 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M36">
-        <v>2.46942</v>
+        <v>2.54205</v>
       </c>
       <c r="N36">
-        <v>1.387246666666667</v>
+        <v>1.314616666666667</v>
       </c>
       <c r="O36">
-        <v>0.2774493333333334</v>
+        <v>0.2629233333333335</v>
       </c>
       <c r="P36">
-        <v>1.109797333333334</v>
+        <v>1.051693333333334</v>
       </c>
       <c r="Q36">
-        <v>1.169797333333334</v>
+        <v>1.111693333333334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07898115683713708</v>
+        <v>0.07941933652465291</v>
       </c>
       <c r="T36">
-        <v>0.6294342840044755</v>
+        <v>0.6377463907592391</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.561770240245348</v>
+        <v>1.517148233381195</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07682256874102439</v>
+        <v>0.09456945535505502</v>
       </c>
       <c r="C37">
-        <v>31.61340738064572</v>
+        <v>13.57105213342597</v>
       </c>
       <c r="D37">
-        <v>52.23840738064572</v>
+        <v>35.00305213342597</v>
       </c>
       <c r="E37">
-        <v>-35.755</v>
+        <v>-34.94799999999999</v>
       </c>
       <c r="F37">
-        <v>28.245</v>
+        <v>29.052</v>
       </c>
       <c r="G37">
         <v>7.62</v>
@@ -4434,45 +4434,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M37">
-        <v>2.54205</v>
+        <v>4.2648336</v>
       </c>
       <c r="N37">
-        <v>1.314616666666667</v>
+        <v>-0.4081669333333333</v>
       </c>
       <c r="O37">
-        <v>0.2629233333333335</v>
+        <v>-0.08163338666666667</v>
       </c>
       <c r="P37">
-        <v>1.051693333333334</v>
+        <v>-0.3265335466666667</v>
       </c>
       <c r="Q37">
-        <v>1.111693333333334</v>
+        <v>-0.2665335466666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07941933652465291</v>
+        <v>0.08012420191461961</v>
       </c>
       <c r="T37">
-        <v>0.6377463907592391</v>
+        <v>0.6511174267430316</v>
       </c>
       <c r="U37">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2</v>
+        <v>0.1808589515270498</v>
       </c>
       <c r="W37">
-        <v>0.07199999999999999</v>
+        <v>0.1202499059158291</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.517148233381195</v>
+        <v>0.904294757635249</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09456945535505502</v>
+        <v>0.09557945535505503</v>
       </c>
       <c r="C38">
-        <v>13.57105213342597</v>
+        <v>12.11890877184916</v>
       </c>
       <c r="D38">
-        <v>35.00305213342597</v>
+        <v>34.35790877184916</v>
       </c>
       <c r="E38">
-        <v>-34.94799999999999</v>
+        <v>-34.141</v>
       </c>
       <c r="F38">
-        <v>29.052</v>
+        <v>29.85899999999999</v>
       </c>
       <c r="G38">
         <v>7.62</v>
@@ -4516,37 +4516,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M38">
-        <v>4.2648336</v>
+        <v>4.3833012</v>
       </c>
       <c r="N38">
-        <v>-0.4081669333333333</v>
+        <v>-0.5266345333333331</v>
       </c>
       <c r="O38">
-        <v>-0.08163338666666667</v>
+        <v>-0.1053269066666666</v>
       </c>
       <c r="P38">
-        <v>-0.3265335466666667</v>
+        <v>-0.4213076266666665</v>
       </c>
       <c r="Q38">
-        <v>-0.2665335466666666</v>
+        <v>-0.3613076266666664</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08012420191461961</v>
+        <v>0.08066903051643898</v>
       </c>
       <c r="T38">
-        <v>0.6511174267430316</v>
+        <v>0.661452623992921</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1808589515270498</v>
+        <v>0.1759708717560485</v>
       </c>
       <c r="W38">
-        <v>0.1202499059158291</v>
+        <v>0.1209674760262121</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.904294757635249</v>
+        <v>0.8798543587802423</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09557945535505503</v>
+        <v>0.09658945535505503</v>
       </c>
       <c r="C39">
-        <v>12.11890877184916</v>
+        <v>10.69011637944246</v>
       </c>
       <c r="D39">
-        <v>34.35790877184916</v>
+        <v>33.73611637944246</v>
       </c>
       <c r="E39">
-        <v>-34.141</v>
+        <v>-33.334</v>
       </c>
       <c r="F39">
-        <v>29.85899999999999</v>
+        <v>30.666</v>
       </c>
       <c r="G39">
         <v>7.62</v>
@@ -4598,37 +4598,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M39">
-        <v>4.3833012</v>
+        <v>4.5017688</v>
       </c>
       <c r="N39">
-        <v>-0.5266345333333331</v>
+        <v>-0.6451021333333329</v>
       </c>
       <c r="O39">
-        <v>-0.1053269066666666</v>
+        <v>-0.1290204266666666</v>
       </c>
       <c r="P39">
-        <v>-0.4213076266666665</v>
+        <v>-0.5160817066666663</v>
       </c>
       <c r="Q39">
-        <v>-0.3613076266666664</v>
+        <v>-0.4560817066666663</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08066903051643898</v>
+        <v>0.08123143423444606</v>
       </c>
       <c r="T39">
-        <v>0.661452623992921</v>
+        <v>0.6721212147024843</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1759708717560485</v>
+        <v>0.1713400593414156</v>
       </c>
       <c r="W39">
-        <v>0.1209674760262121</v>
+        <v>0.1216472792886802</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8798543587802423</v>
+        <v>0.8567002967070781</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09658945535505503</v>
+        <v>0.09759945535505503</v>
       </c>
       <c r="C40">
-        <v>10.69011637944246</v>
+        <v>9.283429709291024</v>
       </c>
       <c r="D40">
-        <v>33.73611637944246</v>
+        <v>33.13642970929102</v>
       </c>
       <c r="E40">
-        <v>-33.334</v>
+        <v>-32.527</v>
       </c>
       <c r="F40">
-        <v>30.666</v>
+        <v>31.473</v>
       </c>
       <c r="G40">
         <v>7.62</v>
@@ -4680,37 +4680,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M40">
-        <v>4.5017688</v>
+        <v>4.6202364</v>
       </c>
       <c r="N40">
-        <v>-0.6451021333333329</v>
+        <v>-0.7635697333333327</v>
       </c>
       <c r="O40">
-        <v>-0.1290204266666666</v>
+        <v>-0.1527139466666665</v>
       </c>
       <c r="P40">
-        <v>-0.5160817066666663</v>
+        <v>-0.6108557866666662</v>
       </c>
       <c r="Q40">
-        <v>-0.4560817066666663</v>
+        <v>-0.5508557866666661</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08123143423444606</v>
+        <v>0.0818122774186173</v>
       </c>
       <c r="T40">
-        <v>0.6721212147024843</v>
+        <v>0.6831395952713775</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1713400593414156</v>
+        <v>0.1669467244865075</v>
       </c>
       <c r="W40">
-        <v>0.1216472792886802</v>
+        <v>0.1222922208453807</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8567002967070781</v>
+        <v>0.8347336224325377</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09759945535505503</v>
+        <v>0.09860945535505503</v>
       </c>
       <c r="C41">
-        <v>9.283429709291024</v>
+        <v>7.89769050915146</v>
       </c>
       <c r="D41">
-        <v>33.13642970929102</v>
+        <v>32.55769050915146</v>
       </c>
       <c r="E41">
-        <v>-32.527</v>
+        <v>-31.72</v>
       </c>
       <c r="F41">
-        <v>31.473</v>
+        <v>32.27999999999999</v>
       </c>
       <c r="G41">
         <v>7.62</v>
@@ -4762,37 +4762,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M41">
-        <v>4.6202364</v>
+        <v>4.738703999999999</v>
       </c>
       <c r="N41">
-        <v>-0.7635697333333327</v>
+        <v>-0.8820373333333325</v>
       </c>
       <c r="O41">
-        <v>-0.1527139466666665</v>
+        <v>-0.1764074666666665</v>
       </c>
       <c r="P41">
-        <v>-0.6108557866666662</v>
+        <v>-0.7056298666666659</v>
       </c>
       <c r="Q41">
-        <v>-0.5508557866666661</v>
+        <v>-0.6456298666666659</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.0818122774186173</v>
+        <v>0.08241248204226093</v>
       </c>
       <c r="T41">
-        <v>0.6831395952713775</v>
+        <v>0.694525255192567</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1669467244865075</v>
+        <v>0.1627730563743449</v>
       </c>
       <c r="W41">
-        <v>0.1222922208453807</v>
+        <v>0.1229049153242462</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8347336224325377</v>
+        <v>0.8138652818717242</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09860945535505503</v>
+        <v>0.1221708817094113</v>
       </c>
       <c r="C42">
-        <v>7.89769050915146</v>
+        <v>-2.334343092708931</v>
       </c>
       <c r="D42">
-        <v>32.55769050915146</v>
+        <v>23.13265690729106</v>
       </c>
       <c r="E42">
-        <v>-31.72</v>
+        <v>-30.913</v>
       </c>
       <c r="F42">
-        <v>32.27999999999999</v>
+        <v>33.087</v>
       </c>
       <c r="G42">
         <v>7.62</v>
@@ -4844,45 +4844,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M42">
-        <v>4.738703999999999</v>
+        <v>6.643869599999999</v>
       </c>
       <c r="N42">
-        <v>-0.8820373333333325</v>
+        <v>-2.787202933333333</v>
       </c>
       <c r="O42">
-        <v>-0.1764074666666665</v>
+        <v>-0.5574405866666665</v>
       </c>
       <c r="P42">
-        <v>-0.7056298666666659</v>
+        <v>-2.229762346666666</v>
       </c>
       <c r="Q42">
-        <v>-0.6456298666666659</v>
+        <v>-2.169762346666666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08241248204226093</v>
+        <v>0.08373036538934381</v>
       </c>
       <c r="T42">
-        <v>0.694525255192567</v>
+        <v>0.7195250152987042</v>
       </c>
       <c r="U42">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1627730563743449</v>
+        <v>0.1160970006595755</v>
       </c>
       <c r="W42">
-        <v>0.1229049153242462</v>
+        <v>0.1774877222675572</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8138652818717242</v>
+        <v>0.5804850032978774</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1221708817094113</v>
+        <v>0.1237208817094113</v>
       </c>
       <c r="C43">
-        <v>-2.334343092708931</v>
+        <v>-3.573649819757815</v>
       </c>
       <c r="D43">
-        <v>23.13265690729106</v>
+        <v>22.70035018024218</v>
       </c>
       <c r="E43">
-        <v>-30.913</v>
+        <v>-30.10599999999999</v>
       </c>
       <c r="F43">
-        <v>33.087</v>
+        <v>33.894</v>
       </c>
       <c r="G43">
         <v>7.62</v>
@@ -4926,37 +4926,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M43">
-        <v>6.643869599999999</v>
+        <v>6.8059152</v>
       </c>
       <c r="N43">
-        <v>-2.787202933333333</v>
+        <v>-2.949248533333333</v>
       </c>
       <c r="O43">
-        <v>-0.5574405866666665</v>
+        <v>-0.5898497066666667</v>
       </c>
       <c r="P43">
-        <v>-2.229762346666666</v>
+        <v>-2.359398826666667</v>
       </c>
       <c r="Q43">
-        <v>-2.169762346666666</v>
+        <v>-2.299398826666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08373036538934381</v>
+        <v>0.08438433720640146</v>
       </c>
       <c r="T43">
-        <v>0.7195250152987042</v>
+        <v>0.7319306190107507</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1160970006595755</v>
+        <v>0.113332786358157</v>
       </c>
       <c r="W43">
-        <v>0.1774877222675572</v>
+        <v>0.1780427764992821</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5804850032978774</v>
+        <v>0.566663931790785</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1237208817094113</v>
+        <v>0.1252708817094113</v>
       </c>
       <c r="C44">
-        <v>-3.573649819757808</v>
+        <v>-4.79709493894244</v>
       </c>
       <c r="D44">
-        <v>22.70035018024218</v>
+        <v>22.28390506105755</v>
       </c>
       <c r="E44">
-        <v>-30.106</v>
+        <v>-29.299</v>
       </c>
       <c r="F44">
-        <v>33.89399999999999</v>
+        <v>34.70099999999999</v>
       </c>
       <c r="G44">
         <v>7.62</v>
@@ -5008,37 +5008,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M44">
-        <v>6.805915199999998</v>
+        <v>6.967960799999999</v>
       </c>
       <c r="N44">
-        <v>-2.949248533333332</v>
+        <v>-3.111294133333332</v>
       </c>
       <c r="O44">
-        <v>-0.5898497066666664</v>
+        <v>-0.6222588266666665</v>
       </c>
       <c r="P44">
-        <v>-2.359398826666665</v>
+        <v>-2.489035306666666</v>
       </c>
       <c r="Q44">
-        <v>-2.299398826666665</v>
+        <v>-2.429035306666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08438433720640146</v>
+        <v>0.08506125540300499</v>
       </c>
       <c r="T44">
-        <v>0.7319306190107506</v>
+        <v>0.7447715070635709</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.113332786358157</v>
+        <v>0.1106971401637813</v>
       </c>
       <c r="W44">
-        <v>0.1780427764992821</v>
+        <v>0.1785720142551127</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5666639317907851</v>
+        <v>0.5534857008189064</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1252708817094113</v>
+        <v>0.1268208817094113</v>
       </c>
       <c r="C45">
-        <v>-4.79709493894244</v>
+        <v>-6.005535682732777</v>
       </c>
       <c r="D45">
-        <v>22.28390506105755</v>
+        <v>21.88246431726722</v>
       </c>
       <c r="E45">
-        <v>-29.299</v>
+        <v>-28.492</v>
       </c>
       <c r="F45">
-        <v>34.70099999999999</v>
+        <v>35.508</v>
       </c>
       <c r="G45">
         <v>7.62</v>
@@ -5090,37 +5090,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M45">
-        <v>6.967960799999999</v>
+        <v>7.130006399999999</v>
       </c>
       <c r="N45">
-        <v>-3.111294133333332</v>
+        <v>-3.273339733333332</v>
       </c>
       <c r="O45">
-        <v>-0.6222588266666665</v>
+        <v>-0.6546679466666665</v>
       </c>
       <c r="P45">
-        <v>-2.489035306666666</v>
+        <v>-2.618671786666666</v>
       </c>
       <c r="Q45">
-        <v>-2.429035306666666</v>
+        <v>-2.558671786666666</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08506125540300499</v>
+        <v>0.08576234924948722</v>
       </c>
       <c r="T45">
-        <v>0.7447715070635709</v>
+        <v>0.7580709982611347</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1106971401637813</v>
+        <v>0.1081812960691499</v>
       </c>
       <c r="W45">
-        <v>0.1785720142551127</v>
+        <v>0.1790771957493147</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5534857008189064</v>
+        <v>0.5409064803457494</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1268208817094113</v>
+        <v>0.1283708817094113</v>
       </c>
       <c r="C46">
-        <v>-6.005535682732777</v>
+        <v>-7.199768605125008</v>
       </c>
       <c r="D46">
-        <v>21.88246431726722</v>
+        <v>21.49523139487499</v>
       </c>
       <c r="E46">
-        <v>-28.492</v>
+        <v>-27.685</v>
       </c>
       <c r="F46">
-        <v>35.508</v>
+        <v>36.315</v>
       </c>
       <c r="G46">
         <v>7.62</v>
@@ -5172,37 +5172,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M46">
-        <v>7.130006399999999</v>
+        <v>7.292052</v>
       </c>
       <c r="N46">
-        <v>-3.273339733333332</v>
+        <v>-3.435385333333333</v>
       </c>
       <c r="O46">
-        <v>-0.6546679466666665</v>
+        <v>-0.6870770666666667</v>
       </c>
       <c r="P46">
-        <v>-2.618671786666666</v>
+        <v>-2.748308266666666</v>
       </c>
       <c r="Q46">
-        <v>-2.558671786666666</v>
+        <v>-2.688308266666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08576234924948722</v>
+        <v>0.08648893741765971</v>
       </c>
       <c r="T46">
-        <v>0.7580709982611347</v>
+        <v>0.7718541073204279</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1081812960691499</v>
+        <v>0.1057772672676132</v>
       </c>
       <c r="W46">
-        <v>0.1790771957493147</v>
+        <v>0.1795599247326633</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5409064803457494</v>
+        <v>0.528886336338066</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1283708817094113</v>
+        <v>0.1299208817094113</v>
       </c>
       <c r="C47">
-        <v>-7.199768605125008</v>
+        <v>-8.380534857129149</v>
       </c>
       <c r="D47">
-        <v>21.49523139487499</v>
+        <v>21.12146514287085</v>
       </c>
       <c r="E47">
-        <v>-27.685</v>
+        <v>-26.87799999999999</v>
       </c>
       <c r="F47">
-        <v>36.315</v>
+        <v>37.122</v>
       </c>
       <c r="G47">
         <v>7.62</v>
@@ -5254,37 +5254,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M47">
-        <v>7.292052</v>
+        <v>7.4540976</v>
       </c>
       <c r="N47">
-        <v>-3.435385333333333</v>
+        <v>-3.597430933333333</v>
       </c>
       <c r="O47">
-        <v>-0.6870770666666667</v>
+        <v>-0.7194861866666666</v>
       </c>
       <c r="P47">
-        <v>-2.748308266666666</v>
+        <v>-2.877944746666667</v>
       </c>
       <c r="Q47">
-        <v>-2.688308266666666</v>
+        <v>-2.817944746666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08648893741765971</v>
+        <v>0.08724243625872749</v>
       </c>
       <c r="T47">
-        <v>0.7718541073204279</v>
+        <v>0.7861477019004359</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1057772672676132</v>
+        <v>0.1034777614574477</v>
       </c>
       <c r="W47">
-        <v>0.1795599247326633</v>
+        <v>0.1800216654993445</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.528886336338066</v>
+        <v>0.5173888072872386</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1299208817094113</v>
+        <v>0.1314708817094113</v>
       </c>
       <c r="C48">
-        <v>-8.380534857129149</v>
+        <v>-9.548524921272012</v>
       </c>
       <c r="D48">
-        <v>21.12146514287085</v>
+        <v>20.76047507872798</v>
       </c>
       <c r="E48">
-        <v>-26.87799999999999</v>
+        <v>-26.071</v>
       </c>
       <c r="F48">
-        <v>37.122</v>
+        <v>37.92899999999999</v>
       </c>
       <c r="G48">
         <v>7.62</v>
@@ -5336,37 +5336,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M48">
-        <v>7.4540976</v>
+        <v>7.616143199999999</v>
       </c>
       <c r="N48">
-        <v>-3.597430933333333</v>
+        <v>-3.759476533333332</v>
       </c>
       <c r="O48">
-        <v>-0.7194861866666666</v>
+        <v>-0.7518953066666665</v>
       </c>
       <c r="P48">
-        <v>-2.877944746666667</v>
+        <v>-3.007581226666665</v>
       </c>
       <c r="Q48">
-        <v>-2.817944746666667</v>
+        <v>-2.947581226666665</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08724243625872749</v>
+        <v>0.08802436901832612</v>
       </c>
       <c r="T48">
-        <v>0.7861477019004359</v>
+        <v>0.8009806774079914</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1034777614574477</v>
+        <v>0.1012761069583531</v>
       </c>
       <c r="W48">
-        <v>0.1800216654993445</v>
+        <v>0.1804637577227627</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5173888072872386</v>
+        <v>0.5063805347917654</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1314708817094113</v>
+        <v>0.1499868972128733</v>
       </c>
       <c r="C49">
-        <v>-9.548524921272012</v>
+        <v>-13.87548191765149</v>
       </c>
       <c r="D49">
-        <v>20.76047507872798</v>
+        <v>17.24051808234851</v>
       </c>
       <c r="E49">
-        <v>-26.071</v>
+        <v>-25.264</v>
       </c>
       <c r="F49">
-        <v>37.92899999999999</v>
+        <v>38.736</v>
       </c>
       <c r="G49">
         <v>7.62</v>
@@ -5418,45 +5418,45 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M49">
-        <v>7.616143199999999</v>
+        <v>9.133948799999999</v>
       </c>
       <c r="N49">
-        <v>-3.759476533333332</v>
+        <v>-5.277282133333332</v>
       </c>
       <c r="O49">
-        <v>-0.7518953066666665</v>
+        <v>-1.055456426666666</v>
       </c>
       <c r="P49">
-        <v>-3.007581226666665</v>
+        <v>-4.221825706666666</v>
       </c>
       <c r="Q49">
-        <v>-2.947581226666665</v>
+        <v>-4.161825706666665</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08802436901832612</v>
+        <v>0.0891556366984132</v>
       </c>
       <c r="T49">
-        <v>0.8009806774079914</v>
+        <v>0.8224404072699734</v>
       </c>
       <c r="U49">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1012761069583531</v>
+        <v>0.08444686413540368</v>
       </c>
       <c r="W49">
-        <v>0.1804637577227627</v>
+        <v>0.2158874294368718</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.5063805347917654</v>
+        <v>0.4222343206770185</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1499868972128733</v>
+        <v>0.1518868972128734</v>
       </c>
       <c r="C50">
-        <v>-13.87548191765148</v>
+        <v>-14.97730769457341</v>
       </c>
       <c r="D50">
-        <v>17.24051808234851</v>
+        <v>16.94569230542658</v>
       </c>
       <c r="E50">
-        <v>-25.264</v>
+        <v>-24.457</v>
       </c>
       <c r="F50">
-        <v>38.73599999999999</v>
+        <v>39.54299999999999</v>
       </c>
       <c r="G50">
         <v>7.62</v>
@@ -5500,37 +5500,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M50">
-        <v>9.133948799999999</v>
+        <v>9.324239399999998</v>
       </c>
       <c r="N50">
-        <v>-5.277282133333332</v>
+        <v>-5.467572733333331</v>
       </c>
       <c r="O50">
-        <v>-1.055456426666666</v>
+        <v>-1.093514546666666</v>
       </c>
       <c r="P50">
-        <v>-4.221825706666666</v>
+        <v>-4.374058186666664</v>
       </c>
       <c r="Q50">
-        <v>-4.161825706666665</v>
+        <v>-4.314058186666664</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0891556366984132</v>
+        <v>0.0900057472219115</v>
       </c>
       <c r="T50">
-        <v>0.8224404072699733</v>
+        <v>0.8385666897654629</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08444686413540368</v>
+        <v>0.08272345874488525</v>
       </c>
       <c r="W50">
-        <v>0.2158874294368718</v>
+        <v>0.2162938084279561</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4222343206770185</v>
+        <v>0.4136172937244262</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1518868972128734</v>
+        <v>0.1537868972128733</v>
       </c>
       <c r="C51">
-        <v>-14.97730769457341</v>
+        <v>-16.06921952404894</v>
       </c>
       <c r="D51">
-        <v>16.94569230542658</v>
+        <v>16.66078047595105</v>
       </c>
       <c r="E51">
-        <v>-24.457</v>
+        <v>-23.65</v>
       </c>
       <c r="F51">
-        <v>39.54299999999999</v>
+        <v>40.34999999999999</v>
       </c>
       <c r="G51">
         <v>7.62</v>
@@ -5582,37 +5582,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M51">
-        <v>9.324239399999998</v>
+        <v>9.514529999999999</v>
       </c>
       <c r="N51">
-        <v>-5.467572733333331</v>
+        <v>-5.657863333333331</v>
       </c>
       <c r="O51">
-        <v>-1.093514546666666</v>
+        <v>-1.131572666666666</v>
       </c>
       <c r="P51">
-        <v>-4.374058186666664</v>
+        <v>-4.526290666666665</v>
       </c>
       <c r="Q51">
-        <v>-4.314058186666664</v>
+        <v>-4.466290666666666</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0900057472219115</v>
+        <v>0.09088986216634973</v>
       </c>
       <c r="T51">
-        <v>0.8385666897654629</v>
+        <v>0.8553380235607723</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08272345874488525</v>
+        <v>0.08106898956998754</v>
       </c>
       <c r="W51">
-        <v>0.2162938084279561</v>
+        <v>0.2166839322593969</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4136172937244262</v>
+        <v>0.4053449478499377</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1537868972128733</v>
+        <v>0.1556868972128733</v>
       </c>
       <c r="C52">
-        <v>-16.06921952404894</v>
+        <v>-17.15170919398329</v>
       </c>
       <c r="D52">
-        <v>16.66078047595105</v>
+        <v>16.38529080601671</v>
       </c>
       <c r="E52">
-        <v>-23.65</v>
+        <v>-22.843</v>
       </c>
       <c r="F52">
-        <v>40.34999999999999</v>
+        <v>41.157</v>
       </c>
       <c r="G52">
         <v>7.62</v>
@@ -5664,37 +5664,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M52">
-        <v>9.514529999999999</v>
+        <v>9.7048206</v>
       </c>
       <c r="N52">
-        <v>-5.657863333333331</v>
+        <v>-5.848153933333332</v>
       </c>
       <c r="O52">
-        <v>-1.131572666666666</v>
+        <v>-1.169630786666666</v>
       </c>
       <c r="P52">
-        <v>-4.526290666666665</v>
+        <v>-4.678523146666666</v>
       </c>
       <c r="Q52">
-        <v>-4.466290666666666</v>
+        <v>-4.618523146666666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09088986216634973</v>
+        <v>0.09181006343505074</v>
       </c>
       <c r="T52">
-        <v>0.8553380235607723</v>
+        <v>0.8727939015926247</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08106898956998754</v>
+        <v>0.07947940153920346</v>
       </c>
       <c r="W52">
-        <v>0.2166839322593969</v>
+        <v>0.2170587571170558</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4053449478499377</v>
+        <v>0.3973970076960174</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1556868972128733</v>
+        <v>0.1575868972128733</v>
       </c>
       <c r="C53">
-        <v>-17.15170919398329</v>
+        <v>-18.22523649409396</v>
       </c>
       <c r="D53">
-        <v>16.38529080601671</v>
+        <v>16.11876350590604</v>
       </c>
       <c r="E53">
-        <v>-22.843</v>
+        <v>-22.03599999999999</v>
       </c>
       <c r="F53">
-        <v>41.157</v>
+        <v>41.964</v>
       </c>
       <c r="G53">
         <v>7.62</v>
@@ -5746,37 +5746,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M53">
-        <v>9.7048206</v>
+        <v>9.895111200000001</v>
       </c>
       <c r="N53">
-        <v>-5.848153933333332</v>
+        <v>-6.038444533333333</v>
       </c>
       <c r="O53">
-        <v>-1.169630786666666</v>
+        <v>-1.207688906666667</v>
       </c>
       <c r="P53">
-        <v>-4.678523146666666</v>
+        <v>-4.830755626666667</v>
       </c>
       <c r="Q53">
-        <v>-4.618523146666666</v>
+        <v>-4.770755626666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09181006343505074</v>
+        <v>0.09276860642328097</v>
       </c>
       <c r="T53">
-        <v>0.8727939015926247</v>
+        <v>0.8909771078758045</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07947940153920346</v>
+        <v>0.07795095150960339</v>
       </c>
       <c r="W53">
-        <v>0.2170587571170558</v>
+        <v>0.2174191656340355</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3973970076960174</v>
+        <v>0.3897547575480169</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1575868972128733</v>
+        <v>0.1594868972128733</v>
       </c>
       <c r="C54">
-        <v>-18.22523649409396</v>
+        <v>-19.29023177670941</v>
       </c>
       <c r="D54">
-        <v>16.11876350590604</v>
+        <v>15.86076822329059</v>
       </c>
       <c r="E54">
-        <v>-22.03599999999999</v>
+        <v>-21.229</v>
       </c>
       <c r="F54">
-        <v>41.964</v>
+        <v>42.77099999999999</v>
       </c>
       <c r="G54">
         <v>7.62</v>
@@ -5828,37 +5828,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M54">
-        <v>9.895111200000001</v>
+        <v>10.0854018</v>
       </c>
       <c r="N54">
-        <v>-6.038444533333333</v>
+        <v>-6.228735133333332</v>
       </c>
       <c r="O54">
-        <v>-1.207688906666667</v>
+        <v>-1.245747026666667</v>
       </c>
       <c r="P54">
-        <v>-4.830755626666667</v>
+        <v>-4.982988106666665</v>
       </c>
       <c r="Q54">
-        <v>-4.770755626666666</v>
+        <v>-4.922988106666665</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09276860642328097</v>
+        <v>0.09376793847484016</v>
       </c>
       <c r="T54">
-        <v>0.8909771078758045</v>
+        <v>0.909934067617843</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07795095150960339</v>
+        <v>0.07648017883961088</v>
       </c>
       <c r="W54">
-        <v>0.2174191656340355</v>
+        <v>0.2177659738296198</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3897547575480169</v>
+        <v>0.3824008941980545</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1594868972128733</v>
+        <v>0.1613868972128733</v>
       </c>
       <c r="C55">
-        <v>-19.29023177670941</v>
+        <v>-20.34709827551466</v>
       </c>
       <c r="D55">
-        <v>15.86076822329059</v>
+        <v>15.61090172448533</v>
       </c>
       <c r="E55">
-        <v>-21.229</v>
+        <v>-20.422</v>
       </c>
       <c r="F55">
-        <v>42.77099999999999</v>
+        <v>43.578</v>
       </c>
       <c r="G55">
         <v>7.62</v>
@@ -5910,37 +5910,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M55">
-        <v>10.0854018</v>
+        <v>10.2756924</v>
       </c>
       <c r="N55">
-        <v>-6.228735133333332</v>
+        <v>-6.419025733333331</v>
       </c>
       <c r="O55">
-        <v>-1.245747026666667</v>
+        <v>-1.283805146666666</v>
       </c>
       <c r="P55">
-        <v>-4.982988106666665</v>
+        <v>-5.135220586666665</v>
       </c>
       <c r="Q55">
-        <v>-4.922988106666665</v>
+        <v>-5.075220586666665</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09376793847484016</v>
+        <v>0.09481071974603233</v>
       </c>
       <c r="T55">
-        <v>0.909934067617843</v>
+        <v>0.9297152430008395</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07648017883961088</v>
+        <v>0.07506387923146994</v>
       </c>
       <c r="W55">
-        <v>0.2177659738296198</v>
+        <v>0.2180999372772194</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3824008941980545</v>
+        <v>0.3753193961573498</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1613868972128733</v>
+        <v>0.1632868972128734</v>
       </c>
       <c r="C56">
-        <v>-20.34709827551466</v>
+        <v>-21.39621420852259</v>
       </c>
       <c r="D56">
-        <v>15.61090172448533</v>
+        <v>15.36878579147741</v>
       </c>
       <c r="E56">
-        <v>-20.422</v>
+        <v>-19.61499999999999</v>
       </c>
       <c r="F56">
-        <v>43.578</v>
+        <v>44.385</v>
       </c>
       <c r="G56">
         <v>7.62</v>
@@ -5992,37 +5992,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M56">
-        <v>10.2756924</v>
+        <v>10.465983</v>
       </c>
       <c r="N56">
-        <v>-6.419025733333331</v>
+        <v>-6.609316333333332</v>
       </c>
       <c r="O56">
-        <v>-1.283805146666666</v>
+        <v>-1.321863266666667</v>
       </c>
       <c r="P56">
-        <v>-5.135220586666665</v>
+        <v>-5.287453066666666</v>
       </c>
       <c r="Q56">
-        <v>-5.075220586666665</v>
+        <v>-5.227453066666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09481071974603233</v>
+        <v>0.09589984685149971</v>
       </c>
       <c r="T56">
-        <v>0.9297152430008395</v>
+        <v>0.9503755817341917</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07506387923146994</v>
+        <v>0.07369908142726138</v>
       </c>
       <c r="W56">
-        <v>0.2180999372772194</v>
+        <v>0.2184217565994518</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3753193961573498</v>
+        <v>0.368495407136307</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1632868972128734</v>
+        <v>0.1651868972128733</v>
       </c>
       <c r="C57">
-        <v>-21.39621420852259</v>
+        <v>-22.43793468833885</v>
       </c>
       <c r="D57">
-        <v>15.36878579147741</v>
+        <v>15.13406531166115</v>
       </c>
       <c r="E57">
-        <v>-19.61499999999999</v>
+        <v>-18.80799999999999</v>
       </c>
       <c r="F57">
-        <v>44.385</v>
+        <v>45.192</v>
       </c>
       <c r="G57">
         <v>7.62</v>
@@ -6074,37 +6074,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M57">
-        <v>10.465983</v>
+        <v>10.6562736</v>
       </c>
       <c r="N57">
-        <v>-6.609316333333332</v>
+        <v>-6.799606933333333</v>
       </c>
       <c r="O57">
-        <v>-1.321863266666667</v>
+        <v>-1.359921386666667</v>
       </c>
       <c r="P57">
-        <v>-5.287453066666666</v>
+        <v>-5.439685546666666</v>
       </c>
       <c r="Q57">
-        <v>-5.227453066666666</v>
+        <v>-5.379685546666666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09589984685149971</v>
+        <v>0.09703847973448834</v>
       </c>
       <c r="T57">
-        <v>0.9503755817341917</v>
+        <v>0.971975026773605</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07369908142726138</v>
+        <v>0.07238302640177458</v>
       </c>
       <c r="W57">
-        <v>0.2184217565994518</v>
+        <v>0.2187320823744615</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.368495407136307</v>
+        <v>0.3619151320088729</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1651868972128733</v>
+        <v>0.1670868972128733</v>
       </c>
       <c r="C58">
-        <v>-22.43793468833885</v>
+        <v>-23.47259346001243</v>
       </c>
       <c r="D58">
-        <v>15.13406531166115</v>
+        <v>14.90640653998757</v>
       </c>
       <c r="E58">
-        <v>-18.80799999999999</v>
+        <v>-18.001</v>
       </c>
       <c r="F58">
-        <v>45.192</v>
+        <v>45.999</v>
       </c>
       <c r="G58">
         <v>7.62</v>
@@ -6156,37 +6156,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M58">
-        <v>10.6562736</v>
+        <v>10.8465642</v>
       </c>
       <c r="N58">
-        <v>-6.799606933333333</v>
+        <v>-6.989897533333332</v>
       </c>
       <c r="O58">
-        <v>-1.359921386666667</v>
+        <v>-1.397979506666666</v>
       </c>
       <c r="P58">
-        <v>-5.439685546666666</v>
+        <v>-5.591918026666666</v>
       </c>
       <c r="Q58">
-        <v>-5.379685546666666</v>
+        <v>-5.531918026666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09703847973448834</v>
+        <v>0.09823007228645317</v>
       </c>
       <c r="T58">
-        <v>0.971975026773605</v>
+        <v>0.9945790971636886</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07238302640177458</v>
+        <v>0.07111314874560309</v>
       </c>
       <c r="W58">
-        <v>0.2187320823744615</v>
+        <v>0.2190315195257868</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3619151320088729</v>
+        <v>0.3555657437280155</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1670868972128733</v>
+        <v>0.1689868972128734</v>
       </c>
       <c r="C59">
-        <v>-23.47259346001243</v>
+        <v>-24.50050448435781</v>
       </c>
       <c r="D59">
-        <v>14.90640653998757</v>
+        <v>14.68549551564219</v>
       </c>
       <c r="E59">
-        <v>-18.001</v>
+        <v>-17.194</v>
       </c>
       <c r="F59">
-        <v>45.999</v>
+        <v>46.806</v>
       </c>
       <c r="G59">
         <v>7.62</v>
@@ -6238,37 +6238,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M59">
-        <v>10.8465642</v>
+        <v>11.0368548</v>
       </c>
       <c r="N59">
-        <v>-6.989897533333332</v>
+        <v>-7.180188133333333</v>
       </c>
       <c r="O59">
-        <v>-1.397979506666666</v>
+        <v>-1.436037626666667</v>
       </c>
       <c r="P59">
-        <v>-5.591918026666666</v>
+        <v>-5.744150506666666</v>
       </c>
       <c r="Q59">
-        <v>-5.531918026666666</v>
+        <v>-5.684150506666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09823007228645317</v>
+        <v>0.09947840734089256</v>
       </c>
       <c r="T59">
-        <v>0.9945790971636886</v>
+        <v>1.018259551858063</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07111314874560309</v>
+        <v>0.06988705997412718</v>
       </c>
       <c r="W59">
-        <v>0.2190315195257868</v>
+        <v>0.2193206312581008</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3555657437280155</v>
+        <v>0.3494352998706359</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1689868972128734</v>
+        <v>0.1708868972128733</v>
       </c>
       <c r="C60">
-        <v>-24.5005044843578</v>
+        <v>-25.52196338254535</v>
       </c>
       <c r="D60">
-        <v>14.68549551564219</v>
+        <v>14.47103661745464</v>
       </c>
       <c r="E60">
-        <v>-17.194</v>
+        <v>-16.387</v>
       </c>
       <c r="F60">
-        <v>46.80599999999999</v>
+        <v>47.61299999999999</v>
       </c>
       <c r="G60">
         <v>7.62</v>
@@ -6320,37 +6320,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M60">
-        <v>11.0368548</v>
+        <v>11.2271454</v>
       </c>
       <c r="N60">
-        <v>-7.180188133333331</v>
+        <v>-7.370478733333332</v>
       </c>
       <c r="O60">
-        <v>-1.436037626666666</v>
+        <v>-1.474095746666666</v>
       </c>
       <c r="P60">
-        <v>-5.744150506666665</v>
+        <v>-5.896382986666666</v>
       </c>
       <c r="Q60">
-        <v>-5.684150506666665</v>
+        <v>-5.836382986666665</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09947840734089254</v>
+        <v>0.1007876367882314</v>
       </c>
       <c r="T60">
-        <v>1.018259551858062</v>
+        <v>1.043095150683869</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06988705997412718</v>
+        <v>0.06870253353388774</v>
       </c>
       <c r="W60">
-        <v>0.2193206312581008</v>
+        <v>0.2195999425927093</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3494352998706359</v>
+        <v>0.3435126676694387</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1708868972128733</v>
+        <v>0.1727868972128733</v>
       </c>
       <c r="C61">
-        <v>-25.52196338254535</v>
+        <v>-26.53724875593753</v>
       </c>
       <c r="D61">
-        <v>14.47103661745464</v>
+        <v>14.26275124406246</v>
       </c>
       <c r="E61">
-        <v>-16.387</v>
+        <v>-15.58</v>
       </c>
       <c r="F61">
-        <v>47.61299999999999</v>
+        <v>48.41999999999999</v>
       </c>
       <c r="G61">
         <v>7.62</v>
@@ -6402,37 +6402,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M61">
-        <v>11.2271454</v>
+        <v>11.417436</v>
       </c>
       <c r="N61">
-        <v>-7.370478733333332</v>
+        <v>-7.560769333333331</v>
       </c>
       <c r="O61">
-        <v>-1.474095746666666</v>
+        <v>-1.512153866666666</v>
       </c>
       <c r="P61">
-        <v>-5.896382986666666</v>
+        <v>-6.048615466666665</v>
       </c>
       <c r="Q61">
-        <v>-5.836382986666665</v>
+        <v>-5.988615466666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1007876367882314</v>
+        <v>0.1021623277079372</v>
       </c>
       <c r="T61">
-        <v>1.043095150683869</v>
+        <v>1.069172529450965</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06870253353388774</v>
+        <v>0.06755749130832295</v>
       </c>
       <c r="W61">
-        <v>0.2195999425927093</v>
+        <v>0.2198699435494974</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3435126676694387</v>
+        <v>0.3377874565416148</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1727868972128733</v>
+        <v>0.1746868972128733</v>
       </c>
       <c r="C62">
-        <v>-26.53724875593753</v>
+        <v>-27.54662339356192</v>
       </c>
       <c r="D62">
-        <v>14.26275124406246</v>
+        <v>14.06037660643807</v>
       </c>
       <c r="E62">
-        <v>-15.58</v>
+        <v>-14.773</v>
       </c>
       <c r="F62">
-        <v>48.41999999999999</v>
+        <v>49.22699999999999</v>
       </c>
       <c r="G62">
         <v>7.62</v>
@@ -6484,37 +6484,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M62">
-        <v>11.417436</v>
+        <v>11.6077266</v>
       </c>
       <c r="N62">
-        <v>-7.560769333333331</v>
+        <v>-7.75105993333333</v>
       </c>
       <c r="O62">
-        <v>-1.512153866666666</v>
+        <v>-1.550211986666666</v>
       </c>
       <c r="P62">
-        <v>-6.048615466666665</v>
+        <v>-6.200847946666665</v>
       </c>
       <c r="Q62">
-        <v>-5.988615466666666</v>
+        <v>-6.140847946666664</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1021623277079372</v>
+        <v>0.1036075155978843</v>
       </c>
       <c r="T62">
-        <v>1.069172529450965</v>
+        <v>1.096587209693298</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06755749130832295</v>
+        <v>0.06644999145080946</v>
       </c>
       <c r="W62">
-        <v>0.2198699435494974</v>
+        <v>0.2201310920158991</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3377874565416148</v>
+        <v>0.3322499572540474</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1746868972128733</v>
+        <v>0.1765868972128734</v>
       </c>
       <c r="C63">
-        <v>-27.54662339356192</v>
+        <v>-28.55033537822517</v>
       </c>
       <c r="D63">
-        <v>14.06037660643807</v>
+        <v>13.86366462177482</v>
       </c>
       <c r="E63">
-        <v>-14.773</v>
+        <v>-13.966</v>
       </c>
       <c r="F63">
-        <v>49.22699999999999</v>
+        <v>50.03399999999999</v>
       </c>
       <c r="G63">
         <v>7.62</v>
@@ -6566,37 +6566,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M63">
-        <v>11.6077266</v>
+        <v>11.7980172</v>
       </c>
       <c r="N63">
-        <v>-7.75105993333333</v>
+        <v>-7.941350533333331</v>
       </c>
       <c r="O63">
-        <v>-1.550211986666666</v>
+        <v>-1.588270106666666</v>
       </c>
       <c r="P63">
-        <v>-6.200847946666665</v>
+        <v>-6.353080426666665</v>
       </c>
       <c r="Q63">
-        <v>-6.140847946666664</v>
+        <v>-6.293080426666664</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1036075155978843</v>
+        <v>0.1051287660083549</v>
       </c>
       <c r="T63">
-        <v>1.096587209693298</v>
+        <v>1.125444767843121</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06644999145080946</v>
+        <v>0.06537821739515125</v>
       </c>
       <c r="W63">
-        <v>0.2201310920158991</v>
+        <v>0.2203838163382233</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3322499572540474</v>
+        <v>0.3268910869757562</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1765868972128734</v>
+        <v>0.1784868972128733</v>
       </c>
       <c r="C64">
-        <v>-28.55033537822517</v>
+        <v>-29.54861910105742</v>
       </c>
       <c r="D64">
-        <v>13.86366462177482</v>
+        <v>13.67238089894258</v>
       </c>
       <c r="E64">
-        <v>-13.966</v>
+        <v>-13.159</v>
       </c>
       <c r="F64">
-        <v>50.03399999999999</v>
+        <v>50.84099999999999</v>
       </c>
       <c r="G64">
         <v>7.62</v>
@@ -6648,37 +6648,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M64">
-        <v>11.7980172</v>
+        <v>11.9883078</v>
       </c>
       <c r="N64">
-        <v>-7.941350533333331</v>
+        <v>-8.131641133333332</v>
       </c>
       <c r="O64">
-        <v>-1.588270106666666</v>
+        <v>-1.626328226666667</v>
       </c>
       <c r="P64">
-        <v>-6.353080426666665</v>
+        <v>-6.505312906666665</v>
       </c>
       <c r="Q64">
-        <v>-6.293080426666664</v>
+        <v>-6.445312906666665</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1051287660083549</v>
+        <v>0.1067322461707429</v>
       </c>
       <c r="T64">
-        <v>1.125444767843121</v>
+        <v>1.155862194001044</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06537821739515125</v>
+        <v>0.06434046791268852</v>
       </c>
       <c r="W64">
-        <v>0.2203838163382233</v>
+        <v>0.220628517666188</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3268910869757562</v>
+        <v>0.3217023395634426</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1784868972128733</v>
+        <v>0.1803868972128733</v>
       </c>
       <c r="C65">
-        <v>-29.54861910105742</v>
+        <v>-30.54169619321078</v>
       </c>
       <c r="D65">
-        <v>13.67238089894258</v>
+        <v>13.48630380678921</v>
       </c>
       <c r="E65">
-        <v>-13.159</v>
+        <v>-12.352</v>
       </c>
       <c r="F65">
-        <v>50.84099999999999</v>
+        <v>51.648</v>
       </c>
       <c r="G65">
         <v>7.62</v>
@@ -6730,37 +6730,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M65">
-        <v>11.9883078</v>
+        <v>12.1785984</v>
       </c>
       <c r="N65">
-        <v>-8.131641133333332</v>
+        <v>-8.321931733333333</v>
       </c>
       <c r="O65">
-        <v>-1.626328226666667</v>
+        <v>-1.664386346666667</v>
       </c>
       <c r="P65">
-        <v>-6.505312906666665</v>
+        <v>-6.657545386666667</v>
       </c>
       <c r="Q65">
-        <v>-6.445312906666665</v>
+        <v>-6.597545386666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1067322461707429</v>
+        <v>0.1084248085643746</v>
       </c>
       <c r="T65">
-        <v>1.155862194001044</v>
+        <v>1.187969477167739</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06434046791268852</v>
+        <v>0.06333514810155276</v>
       </c>
       <c r="W65">
-        <v>0.220628517666188</v>
+        <v>0.2208655720776539</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3217023395634426</v>
+        <v>0.3166757405077638</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1803868972128733</v>
+        <v>0.1822868972128733</v>
       </c>
       <c r="C66">
-        <v>-30.54169619321078</v>
+        <v>-31.52977638249855</v>
       </c>
       <c r="D66">
-        <v>13.48630380678921</v>
+        <v>13.30522361750144</v>
       </c>
       <c r="E66">
-        <v>-12.352</v>
+        <v>-11.545</v>
       </c>
       <c r="F66">
-        <v>51.648</v>
+        <v>52.45499999999999</v>
       </c>
       <c r="G66">
         <v>7.62</v>
@@ -6812,37 +6812,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M66">
-        <v>12.1785984</v>
+        <v>12.368889</v>
       </c>
       <c r="N66">
-        <v>-8.321931733333333</v>
+        <v>-8.51222233333333</v>
       </c>
       <c r="O66">
-        <v>-1.664386346666667</v>
+        <v>-1.702444466666666</v>
       </c>
       <c r="P66">
-        <v>-6.657545386666667</v>
+        <v>-6.809777866666664</v>
       </c>
       <c r="Q66">
-        <v>-6.597545386666667</v>
+        <v>-6.749777866666664</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1084248085643746</v>
+        <v>0.110214088809071</v>
       </c>
       <c r="T66">
-        <v>1.187969477167739</v>
+        <v>1.221911462229675</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06333514810155276</v>
+        <v>0.06236076120768273</v>
       </c>
       <c r="W66">
-        <v>0.2208655720776539</v>
+        <v>0.2210953325072284</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3166757405077638</v>
+        <v>0.3118038060384136</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1822868972128733</v>
+        <v>0.1841868972128734</v>
       </c>
       <c r="C67">
-        <v>-31.52977638249855</v>
+        <v>-32.51305828193627</v>
       </c>
       <c r="D67">
-        <v>13.30522361750144</v>
+        <v>13.12894171806372</v>
       </c>
       <c r="E67">
-        <v>-11.545</v>
+        <v>-10.738</v>
       </c>
       <c r="F67">
-        <v>52.45499999999999</v>
+        <v>53.26199999999999</v>
       </c>
       <c r="G67">
         <v>7.62</v>
@@ -6894,37 +6894,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M67">
-        <v>12.368889</v>
+        <v>12.5591796</v>
       </c>
       <c r="N67">
-        <v>-8.51222233333333</v>
+        <v>-8.702512933333331</v>
       </c>
       <c r="O67">
-        <v>-1.702444466666666</v>
+        <v>-1.740502586666666</v>
       </c>
       <c r="P67">
-        <v>-6.809777866666664</v>
+        <v>-6.962010346666665</v>
       </c>
       <c r="Q67">
-        <v>-6.749777866666664</v>
+        <v>-6.902010346666664</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.110214088809071</v>
+        <v>0.1121086208328673</v>
       </c>
       <c r="T67">
-        <v>1.221911462229675</v>
+        <v>1.257850034648195</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06236076120768273</v>
+        <v>0.0614159011893845</v>
       </c>
       <c r="W67">
-        <v>0.2210953325072284</v>
+        <v>0.2213181304995432</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3118038060384136</v>
+        <v>0.3070795059469225</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1841868972128734</v>
+        <v>0.1860868972128733</v>
       </c>
       <c r="C68">
-        <v>-32.51305828193627</v>
+        <v>-33.49173011641793</v>
       </c>
       <c r="D68">
-        <v>13.12894171806372</v>
+        <v>12.95726988358207</v>
       </c>
       <c r="E68">
-        <v>-10.738</v>
+        <v>-9.930999999999997</v>
       </c>
       <c r="F68">
-        <v>53.26199999999999</v>
+        <v>54.069</v>
       </c>
       <c r="G68">
         <v>7.62</v>
@@ -6976,37 +6976,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M68">
-        <v>12.5591796</v>
+        <v>12.7494702</v>
       </c>
       <c r="N68">
-        <v>-8.702512933333331</v>
+        <v>-8.892803533333332</v>
       </c>
       <c r="O68">
-        <v>-1.740502586666666</v>
+        <v>-1.778560706666666</v>
       </c>
       <c r="P68">
-        <v>-6.962010346666665</v>
+        <v>-7.114242826666666</v>
       </c>
       <c r="Q68">
-        <v>-6.902010346666664</v>
+        <v>-7.054242826666666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1121086208328673</v>
+        <v>0.1141179729793178</v>
       </c>
       <c r="T68">
-        <v>1.257850034648195</v>
+        <v>1.295966702364807</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0614159011893845</v>
+        <v>0.06049924594775189</v>
       </c>
       <c r="W68">
-        <v>0.2213181304995432</v>
+        <v>0.2215342778055201</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3070795059469225</v>
+        <v>0.3024962297387594</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1860868972128733</v>
+        <v>0.1879868972128734</v>
       </c>
       <c r="C69">
-        <v>-33.49173011641793</v>
+        <v>-34.4659703931165</v>
       </c>
       <c r="D69">
-        <v>12.95726988358207</v>
+        <v>12.7900296068835</v>
       </c>
       <c r="E69">
-        <v>-9.930999999999997</v>
+        <v>-9.123999999999995</v>
       </c>
       <c r="F69">
-        <v>54.069</v>
+        <v>54.876</v>
       </c>
       <c r="G69">
         <v>7.62</v>
@@ -7058,37 +7058,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M69">
-        <v>12.7494702</v>
+        <v>12.9397608</v>
       </c>
       <c r="N69">
-        <v>-8.892803533333332</v>
+        <v>-9.083094133333333</v>
       </c>
       <c r="O69">
-        <v>-1.778560706666666</v>
+        <v>-1.816618826666667</v>
       </c>
       <c r="P69">
-        <v>-7.114242826666666</v>
+        <v>-7.266475306666666</v>
       </c>
       <c r="Q69">
-        <v>-7.054242826666666</v>
+        <v>-7.206475306666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1141179729793178</v>
+        <v>0.1162529096349215</v>
       </c>
       <c r="T69">
-        <v>1.295966702364807</v>
+        <v>1.336465661813707</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06049924594775189</v>
+        <v>0.05960955115440258</v>
       </c>
       <c r="W69">
-        <v>0.2215342778055201</v>
+        <v>0.2217440678377919</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3024962297387594</v>
+        <v>0.298047755772013</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1879868972128734</v>
+        <v>0.1898868972128734</v>
       </c>
       <c r="C70">
-        <v>-34.4659703931165</v>
+        <v>-35.43594852062874</v>
       </c>
       <c r="D70">
-        <v>12.7900296068835</v>
+        <v>12.62705147937125</v>
       </c>
       <c r="E70">
-        <v>-9.123999999999995</v>
+        <v>-8.316999999999993</v>
       </c>
       <c r="F70">
-        <v>54.876</v>
+        <v>55.683</v>
       </c>
       <c r="G70">
         <v>7.62</v>
@@ -7140,37 +7140,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M70">
-        <v>12.9397608</v>
+        <v>13.1300514</v>
       </c>
       <c r="N70">
-        <v>-9.083094133333333</v>
+        <v>-9.273384733333334</v>
       </c>
       <c r="O70">
-        <v>-1.816618826666667</v>
+        <v>-1.854676946666667</v>
       </c>
       <c r="P70">
-        <v>-7.266475306666666</v>
+        <v>-7.418707786666667</v>
       </c>
       <c r="Q70">
-        <v>-7.206475306666666</v>
+        <v>-7.358707786666667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1162529096349215</v>
+        <v>0.1185255841392738</v>
       </c>
       <c r="T70">
-        <v>1.336465661813707</v>
+        <v>1.379577457356084</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05960955115440258</v>
+        <v>0.05874564461593298</v>
       </c>
       <c r="W70">
-        <v>0.2217440678377919</v>
+        <v>0.221947776999563</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.298047755772013</v>
+        <v>0.293728223079665</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1898868972128734</v>
+        <v>0.1917868972128733</v>
       </c>
       <c r="C71">
-        <v>-35.43594852062874</v>
+        <v>-36.40182538137855</v>
       </c>
       <c r="D71">
-        <v>12.62705147937125</v>
+        <v>12.46817461862144</v>
       </c>
       <c r="E71">
-        <v>-8.316999999999993</v>
+        <v>-7.509999999999998</v>
       </c>
       <c r="F71">
-        <v>55.683</v>
+        <v>56.48999999999999</v>
       </c>
       <c r="G71">
         <v>7.62</v>
@@ -7222,37 +7222,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M71">
-        <v>13.1300514</v>
+        <v>13.320342</v>
       </c>
       <c r="N71">
-        <v>-9.273384733333334</v>
+        <v>-9.463675333333333</v>
       </c>
       <c r="O71">
-        <v>-1.854676946666667</v>
+        <v>-1.892735066666667</v>
       </c>
       <c r="P71">
-        <v>-7.418707786666667</v>
+        <v>-7.570940266666666</v>
       </c>
       <c r="Q71">
-        <v>-7.358707786666667</v>
+        <v>-7.510940266666665</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1185255841392738</v>
+        <v>0.1209497702772496</v>
       </c>
       <c r="T71">
-        <v>1.379577457356084</v>
+        <v>1.425563372601287</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05874564461593298</v>
+        <v>0.05790642112141967</v>
       </c>
       <c r="W71">
-        <v>0.221947776999563</v>
+        <v>0.2221456658995692</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.293728223079665</v>
+        <v>0.2895321056070983</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1917868972128733</v>
+        <v>0.1936868972128734</v>
       </c>
       <c r="C72">
-        <v>-36.40182538137855</v>
+        <v>-37.36375386134438</v>
       </c>
       <c r="D72">
-        <v>12.46817461862144</v>
+        <v>12.31324613865562</v>
       </c>
       <c r="E72">
-        <v>-7.509999999999998</v>
+        <v>-6.702999999999996</v>
       </c>
       <c r="F72">
-        <v>56.48999999999999</v>
+        <v>57.297</v>
       </c>
       <c r="G72">
         <v>7.62</v>
@@ -7304,37 +7304,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M72">
-        <v>13.320342</v>
+        <v>13.5106326</v>
       </c>
       <c r="N72">
-        <v>-9.463675333333333</v>
+        <v>-9.653965933333332</v>
       </c>
       <c r="O72">
-        <v>-1.892735066666667</v>
+        <v>-1.930793186666667</v>
       </c>
       <c r="P72">
-        <v>-7.570940266666666</v>
+        <v>-7.723172746666665</v>
       </c>
       <c r="Q72">
-        <v>-7.510940266666665</v>
+        <v>-7.663172746666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1209497702772496</v>
+        <v>0.1235411416661203</v>
       </c>
       <c r="T72">
-        <v>1.425563372601287</v>
+        <v>1.474720730277194</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05790642112141967</v>
+        <v>0.05709083772534333</v>
       </c>
       <c r="W72">
-        <v>0.2221456658995692</v>
+        <v>0.2223379804643641</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2895321056070983</v>
+        <v>0.2854541886267167</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1936868972128734</v>
+        <v>0.1955868972128733</v>
       </c>
       <c r="C73">
-        <v>-37.36375386134437</v>
+        <v>-38.32187934077743</v>
       </c>
       <c r="D73">
-        <v>12.31324613865562</v>
+        <v>12.16212065922256</v>
       </c>
       <c r="E73">
-        <v>-6.703000000000003</v>
+        <v>-5.896000000000001</v>
       </c>
       <c r="F73">
-        <v>57.29699999999999</v>
+        <v>58.10399999999999</v>
       </c>
       <c r="G73">
         <v>7.62</v>
@@ -7386,37 +7386,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M73">
-        <v>13.5106326</v>
+        <v>13.7009232</v>
       </c>
       <c r="N73">
-        <v>-9.65396593333333</v>
+        <v>-9.844256533333331</v>
       </c>
       <c r="O73">
-        <v>-1.930793186666666</v>
+        <v>-1.968851306666666</v>
       </c>
       <c r="P73">
-        <v>-7.723172746666664</v>
+        <v>-7.875405226666665</v>
       </c>
       <c r="Q73">
-        <v>-7.663172746666664</v>
+        <v>-7.815405226666664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1235411416661202</v>
+        <v>0.1263176110113388</v>
       </c>
       <c r="T73">
-        <v>1.474720730277194</v>
+        <v>1.527389327787093</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05709083772534334</v>
+        <v>0.05629790942360246</v>
       </c>
       <c r="W73">
-        <v>0.2223379804643641</v>
+        <v>0.2225249529579146</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2854541886267167</v>
+        <v>0.2814895471180123</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1955868972128733</v>
+        <v>0.1974868972128733</v>
       </c>
       <c r="C74">
-        <v>-38.32187934077743</v>
+        <v>-39.27634014922127</v>
       </c>
       <c r="D74">
-        <v>12.16212065922256</v>
+        <v>12.01465985077871</v>
       </c>
       <c r="E74">
-        <v>-5.896000000000001</v>
+        <v>-5.089000000000006</v>
       </c>
       <c r="F74">
-        <v>58.10399999999999</v>
+        <v>58.91099999999999</v>
       </c>
       <c r="G74">
         <v>7.62</v>
@@ -7468,37 +7468,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M74">
-        <v>13.7009232</v>
+        <v>13.8912138</v>
       </c>
       <c r="N74">
-        <v>-9.844256533333331</v>
+        <v>-10.03454713333333</v>
       </c>
       <c r="O74">
-        <v>-1.968851306666666</v>
+        <v>-2.006909426666666</v>
       </c>
       <c r="P74">
-        <v>-7.875405226666665</v>
+        <v>-8.027637706666663</v>
       </c>
       <c r="Q74">
-        <v>-7.815405226666664</v>
+        <v>-7.967637706666663</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1263176110113388</v>
+        <v>0.1292997447524995</v>
       </c>
       <c r="T74">
-        <v>1.527389327787093</v>
+        <v>1.583959302890319</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05629790942360246</v>
+        <v>0.05552670518492298</v>
       </c>
       <c r="W74">
-        <v>0.2225249529579146</v>
+        <v>0.2227068029173952</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2814895471180123</v>
+        <v>0.2776335259246149</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1974868972128733</v>
+        <v>0.1993868972128733</v>
       </c>
       <c r="C75">
-        <v>-39.27634014922127</v>
+        <v>-40.22726798782629</v>
       </c>
       <c r="D75">
-        <v>12.01465985077871</v>
+        <v>11.8707320121737</v>
       </c>
       <c r="E75">
-        <v>-5.089000000000006</v>
+        <v>-4.282000000000004</v>
       </c>
       <c r="F75">
-        <v>58.91099999999999</v>
+        <v>59.71799999999999</v>
       </c>
       <c r="G75">
         <v>7.62</v>
@@ -7550,37 +7550,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M75">
-        <v>13.8912138</v>
+        <v>14.0815044</v>
       </c>
       <c r="N75">
-        <v>-10.03454713333333</v>
+        <v>-10.22483773333333</v>
       </c>
       <c r="O75">
-        <v>-2.006909426666666</v>
+        <v>-2.044967546666666</v>
       </c>
       <c r="P75">
-        <v>-8.027637706666663</v>
+        <v>-8.179870186666665</v>
       </c>
       <c r="Q75">
-        <v>-7.967637706666663</v>
+        <v>-8.119870186666665</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1292997447524995</v>
+        <v>0.1325112733968264</v>
       </c>
       <c r="T75">
-        <v>1.583959302890319</v>
+        <v>1.644880814539947</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05552670518492298</v>
+        <v>0.05477634430404563</v>
       </c>
       <c r="W75">
-        <v>0.2227068029173952</v>
+        <v>0.222883738013106</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2776335259246149</v>
+        <v>0.2738817215202282</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1993868972128733</v>
+        <v>0.2012868972128734</v>
       </c>
       <c r="C76">
-        <v>-40.22726798782629</v>
+        <v>-41.17478832166928</v>
       </c>
       <c r="D76">
-        <v>11.8707320121737</v>
+        <v>11.7302116783307</v>
       </c>
       <c r="E76">
-        <v>-4.282000000000004</v>
+        <v>-3.475000000000001</v>
       </c>
       <c r="F76">
-        <v>59.71799999999999</v>
+        <v>60.52499999999999</v>
       </c>
       <c r="G76">
         <v>7.62</v>
@@ -7632,37 +7632,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M76">
-        <v>14.0815044</v>
+        <v>14.271795</v>
       </c>
       <c r="N76">
-        <v>-10.22483773333333</v>
+        <v>-10.41512833333333</v>
       </c>
       <c r="O76">
-        <v>-2.044967546666666</v>
+        <v>-2.083025666666666</v>
       </c>
       <c r="P76">
-        <v>-8.179870186666665</v>
+        <v>-8.332102666666666</v>
       </c>
       <c r="Q76">
-        <v>-8.119870186666665</v>
+        <v>-8.272102666666665</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1325112733968264</v>
+        <v>0.1359797243326995</v>
       </c>
       <c r="T76">
-        <v>1.644880814539947</v>
+        <v>1.710676047121545</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05477634430404563</v>
+        <v>0.05404599304665835</v>
       </c>
       <c r="W76">
-        <v>0.222883738013106</v>
+        <v>0.223055954839598</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2738817215202282</v>
+        <v>0.2702299652332918</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2012868972128734</v>
+        <v>0.2031868972128734</v>
       </c>
       <c r="C77">
-        <v>-41.17478832166928</v>
+        <v>-42.1190207445344</v>
       </c>
       <c r="D77">
-        <v>11.7302116783307</v>
+        <v>11.5929792554656</v>
       </c>
       <c r="E77">
-        <v>-3.475000000000001</v>
+        <v>-2.667999999999999</v>
       </c>
       <c r="F77">
-        <v>60.52499999999999</v>
+        <v>61.33199999999999</v>
       </c>
       <c r="G77">
         <v>7.62</v>
@@ -7714,37 +7714,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M77">
-        <v>14.271795</v>
+        <v>14.4620856</v>
       </c>
       <c r="N77">
-        <v>-10.41512833333333</v>
+        <v>-10.60541893333333</v>
       </c>
       <c r="O77">
-        <v>-2.083025666666666</v>
+        <v>-2.121083786666666</v>
       </c>
       <c r="P77">
-        <v>-8.332102666666666</v>
+        <v>-8.484335146666664</v>
       </c>
       <c r="Q77">
-        <v>-8.272102666666665</v>
+        <v>-8.424335146666664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1359797243326995</v>
+        <v>0.139737212846562</v>
       </c>
       <c r="T77">
-        <v>1.710676047121545</v>
+        <v>1.781954215751609</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05404599304665835</v>
+        <v>0.05333486155920233</v>
       </c>
       <c r="W77">
-        <v>0.223055954839598</v>
+        <v>0.2232236396443401</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2702299652332918</v>
+        <v>0.2666743077960116</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2031868972128734</v>
+        <v>0.2050868972128733</v>
       </c>
       <c r="C78">
-        <v>-42.1190207445344</v>
+        <v>-43.06007931838452</v>
       </c>
       <c r="D78">
-        <v>11.5929792554656</v>
+        <v>11.45892068161548</v>
       </c>
       <c r="E78">
-        <v>-2.667999999999999</v>
+        <v>-1.860999999999997</v>
       </c>
       <c r="F78">
-        <v>61.33199999999999</v>
+        <v>62.139</v>
       </c>
       <c r="G78">
         <v>7.62</v>
@@ -7796,37 +7796,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M78">
-        <v>14.4620856</v>
+        <v>14.6523762</v>
       </c>
       <c r="N78">
-        <v>-10.60541893333333</v>
+        <v>-10.79570953333333</v>
       </c>
       <c r="O78">
-        <v>-2.121083786666666</v>
+        <v>-2.159141906666667</v>
       </c>
       <c r="P78">
-        <v>-8.484335146666664</v>
+        <v>-8.636567626666665</v>
       </c>
       <c r="Q78">
-        <v>-8.424335146666664</v>
+        <v>-8.576567626666664</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.139737212846562</v>
+        <v>0.1438214394920647</v>
       </c>
       <c r="T78">
-        <v>1.781954215751609</v>
+        <v>1.859430486001679</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05333486155920233</v>
+        <v>0.05264220101947242</v>
       </c>
       <c r="W78">
-        <v>0.2232236396443401</v>
+        <v>0.2233869689996084</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2666743077960116</v>
+        <v>0.2632110050973622</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2050868972128733</v>
+        <v>0.2069868972128733</v>
       </c>
       <c r="C79">
-        <v>-43.06007931838452</v>
+        <v>-43.99807288954866</v>
       </c>
       <c r="D79">
-        <v>11.45892068161548</v>
+        <v>11.32792711045133</v>
       </c>
       <c r="E79">
-        <v>-1.860999999999997</v>
+        <v>-1.054000000000002</v>
       </c>
       <c r="F79">
-        <v>62.139</v>
+        <v>62.94599999999999</v>
       </c>
       <c r="G79">
         <v>7.62</v>
@@ -7878,37 +7878,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M79">
-        <v>14.6523762</v>
+        <v>14.8426668</v>
       </c>
       <c r="N79">
-        <v>-10.79570953333333</v>
+        <v>-10.98600013333333</v>
       </c>
       <c r="O79">
-        <v>-2.159141906666667</v>
+        <v>-2.197200026666666</v>
       </c>
       <c r="P79">
-        <v>-8.636567626666665</v>
+        <v>-8.788800106666665</v>
       </c>
       <c r="Q79">
-        <v>-8.576567626666664</v>
+        <v>-8.728800106666665</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1438214394920647</v>
+        <v>0.1482769594689767</v>
       </c>
       <c r="T79">
-        <v>1.859430486001679</v>
+        <v>1.94395005354721</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05264220101947242</v>
+        <v>0.05196730100640227</v>
       </c>
       <c r="W79">
-        <v>0.2233869689996084</v>
+        <v>0.2235461104226904</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2632110050973622</v>
+        <v>0.2598365050320114</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2069868972128733</v>
+        <v>0.2088868972128733</v>
       </c>
       <c r="C80">
-        <v>-43.99807288954866</v>
+        <v>-44.93310538346718</v>
       </c>
       <c r="D80">
-        <v>11.32792711045133</v>
+        <v>11.19989461653281</v>
       </c>
       <c r="E80">
-        <v>-1.054000000000002</v>
+        <v>-0.2469999999999999</v>
       </c>
       <c r="F80">
-        <v>62.94599999999999</v>
+        <v>63.75299999999999</v>
       </c>
       <c r="G80">
         <v>7.62</v>
@@ -7960,37 +7960,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M80">
-        <v>14.8426668</v>
+        <v>15.0329574</v>
       </c>
       <c r="N80">
-        <v>-10.98600013333333</v>
+        <v>-11.17629073333333</v>
       </c>
       <c r="O80">
-        <v>-2.197200026666666</v>
+        <v>-2.235258146666666</v>
       </c>
       <c r="P80">
-        <v>-8.788800106666665</v>
+        <v>-8.941032586666665</v>
       </c>
       <c r="Q80">
-        <v>-8.728800106666665</v>
+        <v>-8.881032586666665</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1482769594689767</v>
+        <v>0.1531568146817851</v>
       </c>
       <c r="T80">
-        <v>1.94395005354721</v>
+        <v>2.036519103716125</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05196730100640227</v>
+        <v>0.05130948706961236</v>
       </c>
       <c r="W80">
-        <v>0.2235461104226904</v>
+        <v>0.2237012229489854</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2598365050320114</v>
+        <v>0.2565474353480618</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2088868972128733</v>
+        <v>0.2107868972128734</v>
       </c>
       <c r="C81">
-        <v>-44.93310538346718</v>
+        <v>-45.86527607967252</v>
       </c>
       <c r="D81">
-        <v>11.19989461653281</v>
+        <v>11.07472392032747</v>
       </c>
       <c r="E81">
-        <v>-0.2469999999999999</v>
+        <v>0.5599999999999952</v>
       </c>
       <c r="F81">
-        <v>63.75299999999999</v>
+        <v>64.55999999999999</v>
       </c>
       <c r="G81">
         <v>7.62</v>
@@ -8042,37 +8042,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M81">
-        <v>15.0329574</v>
+        <v>15.223248</v>
       </c>
       <c r="N81">
-        <v>-11.17629073333333</v>
+        <v>-11.36658133333333</v>
       </c>
       <c r="O81">
-        <v>-2.235258146666666</v>
+        <v>-2.273316266666666</v>
       </c>
       <c r="P81">
-        <v>-8.941032586666665</v>
+        <v>-9.093265066666664</v>
       </c>
       <c r="Q81">
-        <v>-8.881032586666665</v>
+        <v>-9.033265066666663</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1531568146817851</v>
+        <v>0.1585246554158743</v>
       </c>
       <c r="T81">
-        <v>2.036519103716125</v>
+        <v>2.138345058901931</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05130948706961236</v>
+        <v>0.05066811848124221</v>
       </c>
       <c r="W81">
-        <v>0.2237012229489854</v>
+        <v>0.2238524576621231</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2565474353480618</v>
+        <v>0.2533405924062111</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2107868972128734</v>
+        <v>0.2126868972128733</v>
       </c>
       <c r="C82">
-        <v>-45.86527607967252</v>
+        <v>-46.79467986853456</v>
       </c>
       <c r="D82">
-        <v>11.07472392032747</v>
+        <v>10.95232013146543</v>
       </c>
       <c r="E82">
-        <v>0.5599999999999952</v>
+        <v>1.366999999999997</v>
       </c>
       <c r="F82">
-        <v>64.55999999999999</v>
+        <v>65.36699999999999</v>
       </c>
       <c r="G82">
         <v>7.62</v>
@@ -8124,37 +8124,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M82">
-        <v>15.223248</v>
+        <v>15.4135386</v>
       </c>
       <c r="N82">
-        <v>-11.36658133333333</v>
+        <v>-11.55687193333333</v>
       </c>
       <c r="O82">
-        <v>-2.273316266666666</v>
+        <v>-2.311374386666667</v>
       </c>
       <c r="P82">
-        <v>-9.093265066666664</v>
+        <v>-9.245497546666666</v>
       </c>
       <c r="Q82">
-        <v>-9.033265066666663</v>
+        <v>-9.185497546666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1585246554158743</v>
+        <v>0.1644575320167099</v>
       </c>
       <c r="T82">
-        <v>2.138345058901931</v>
+        <v>2.250889535686244</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05066811848124221</v>
+        <v>0.05004258615431328</v>
       </c>
       <c r="W82">
-        <v>0.2238524576621231</v>
+        <v>0.2239999581848129</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2533405924062111</v>
+        <v>0.2502129307715665</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2126868972128733</v>
+        <v>0.2145868972128734</v>
       </c>
       <c r="C83">
-        <v>-46.79467986853456</v>
+        <v>-47.72140749116598</v>
       </c>
       <c r="D83">
-        <v>10.95232013146543</v>
+        <v>10.83259250883402</v>
       </c>
       <c r="E83">
-        <v>1.366999999999997</v>
+        <v>2.173999999999999</v>
       </c>
       <c r="F83">
-        <v>65.36699999999999</v>
+        <v>66.17399999999999</v>
       </c>
       <c r="G83">
         <v>7.62</v>
@@ -8206,37 +8206,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M83">
-        <v>15.4135386</v>
+        <v>15.6038292</v>
       </c>
       <c r="N83">
-        <v>-11.55687193333333</v>
+        <v>-11.74716253333333</v>
       </c>
       <c r="O83">
-        <v>-2.311374386666667</v>
+        <v>-2.349432506666666</v>
       </c>
       <c r="P83">
-        <v>-9.245497546666666</v>
+        <v>-9.397730026666665</v>
       </c>
       <c r="Q83">
-        <v>-9.185497546666666</v>
+        <v>-9.337730026666664</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1644575320167099</v>
+        <v>0.1710496171287493</v>
       </c>
       <c r="T83">
-        <v>2.250889535686244</v>
+        <v>2.375938954335479</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05004258615431328</v>
+        <v>0.04943231071340703</v>
       </c>
       <c r="W83">
-        <v>0.2239999581848129</v>
+        <v>0.2241438611337786</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2502129307715665</v>
+        <v>0.2471615535670352</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2145868972128734</v>
+        <v>0.2164868972128733</v>
       </c>
       <c r="C84">
-        <v>-47.72140749116598</v>
+        <v>-48.64554576376218</v>
       </c>
       <c r="D84">
-        <v>10.83259250883402</v>
+        <v>10.71545423623781</v>
       </c>
       <c r="E84">
-        <v>2.173999999999999</v>
+        <v>2.981000000000002</v>
       </c>
       <c r="F84">
-        <v>66.17399999999999</v>
+        <v>66.98099999999999</v>
       </c>
       <c r="G84">
         <v>7.62</v>
@@ -8288,37 +8288,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M84">
-        <v>15.6038292</v>
+        <v>15.7941198</v>
       </c>
       <c r="N84">
-        <v>-11.74716253333333</v>
+        <v>-11.93745313333333</v>
       </c>
       <c r="O84">
-        <v>-2.349432506666666</v>
+        <v>-2.387490626666666</v>
       </c>
       <c r="P84">
-        <v>-9.397730026666665</v>
+        <v>-9.549962506666665</v>
       </c>
       <c r="Q84">
-        <v>-9.337730026666664</v>
+        <v>-9.489962506666664</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1710496171287493</v>
+        <v>0.1784172416657346</v>
       </c>
       <c r="T84">
-        <v>2.375938954335479</v>
+        <v>2.51570006929639</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04943231071340703</v>
+        <v>0.04883674070481177</v>
       </c>
       <c r="W84">
-        <v>0.2241438611337786</v>
+        <v>0.2242842965418054</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2471615535670352</v>
+        <v>0.2441837035240588</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2164868972128733</v>
+        <v>0.2183868972128734</v>
       </c>
       <c r="C85">
-        <v>-48.64554576376218</v>
+        <v>-49.56717778754171</v>
       </c>
       <c r="D85">
-        <v>10.71545423623781</v>
+        <v>10.60082221245828</v>
       </c>
       <c r="E85">
-        <v>2.981000000000002</v>
+        <v>3.788000000000004</v>
       </c>
       <c r="F85">
-        <v>66.98099999999999</v>
+        <v>67.788</v>
       </c>
       <c r="G85">
         <v>7.62</v>
@@ -8370,37 +8370,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M85">
-        <v>15.7941198</v>
+        <v>15.9844104</v>
       </c>
       <c r="N85">
-        <v>-11.93745313333333</v>
+        <v>-12.12774373333333</v>
       </c>
       <c r="O85">
-        <v>-2.387490626666666</v>
+        <v>-2.425548746666667</v>
       </c>
       <c r="P85">
-        <v>-9.549962506666665</v>
+        <v>-9.702194986666665</v>
       </c>
       <c r="Q85">
-        <v>-9.489962506666664</v>
+        <v>-9.642194986666665</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1784172416657346</v>
+        <v>0.186705819269843</v>
       </c>
       <c r="T85">
-        <v>2.51570006929639</v>
+        <v>2.672931323627415</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04883674070481177</v>
+        <v>0.04825535093451638</v>
       </c>
       <c r="W85">
-        <v>0.2242842965418054</v>
+        <v>0.2244213882496411</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2441837035240588</v>
+        <v>0.2412767546725819</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2183868972128734</v>
+        <v>0.2202868972128733</v>
       </c>
       <c r="C86">
-        <v>-49.56717778754171</v>
+        <v>-50.4863831453538</v>
       </c>
       <c r="D86">
-        <v>10.60082221245827</v>
+        <v>10.48861685464618</v>
       </c>
       <c r="E86">
-        <v>3.78799999999999</v>
+        <v>4.594999999999992</v>
       </c>
       <c r="F86">
-        <v>67.78799999999998</v>
+        <v>68.59499999999998</v>
       </c>
       <c r="G86">
         <v>7.62</v>
@@ -8452,37 +8452,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M86">
-        <v>15.9844104</v>
+        <v>16.174701</v>
       </c>
       <c r="N86">
-        <v>-12.12774373333333</v>
+        <v>-12.31803433333333</v>
       </c>
       <c r="O86">
-        <v>-2.425548746666666</v>
+        <v>-2.463606866666666</v>
       </c>
       <c r="P86">
-        <v>-9.702194986666663</v>
+        <v>-9.854427466666662</v>
       </c>
       <c r="Q86">
-        <v>-9.642194986666663</v>
+        <v>-9.794427466666662</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1867058192698429</v>
+        <v>0.1960995405544991</v>
       </c>
       <c r="T86">
-        <v>2.672931323627413</v>
+        <v>2.851126745202574</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0482553509345164</v>
+        <v>0.04768764092352209</v>
       </c>
       <c r="W86">
-        <v>0.2244213882496411</v>
+        <v>0.2245552542702335</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.241276754672582</v>
+        <v>0.2384382046176104</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2202868972128733</v>
+        <v>0.2221868972128734</v>
       </c>
       <c r="C87">
-        <v>-50.4863831453538</v>
+        <v>-51.40323808593061</v>
       </c>
       <c r="D87">
-        <v>10.48861685464618</v>
+        <v>10.37876191406938</v>
       </c>
       <c r="E87">
-        <v>4.594999999999992</v>
+        <v>5.401999999999994</v>
       </c>
       <c r="F87">
-        <v>68.59499999999998</v>
+        <v>69.40199999999999</v>
       </c>
       <c r="G87">
         <v>7.62</v>
@@ -8534,37 +8534,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M87">
-        <v>16.174701</v>
+        <v>16.3649916</v>
       </c>
       <c r="N87">
-        <v>-12.31803433333333</v>
+        <v>-12.50832493333333</v>
       </c>
       <c r="O87">
-        <v>-2.463606866666666</v>
+        <v>-2.501664986666666</v>
       </c>
       <c r="P87">
-        <v>-9.854427466666662</v>
+        <v>-10.00665994666666</v>
       </c>
       <c r="Q87">
-        <v>-9.794427466666662</v>
+        <v>-9.946659946666662</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1960995405544991</v>
+        <v>0.2068352220226776</v>
       </c>
       <c r="T87">
-        <v>2.851126745202574</v>
+        <v>3.054778655574186</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04768764092352209</v>
+        <v>0.04713313347092299</v>
       </c>
       <c r="W87">
-        <v>0.2245552542702335</v>
+        <v>0.2246860071275564</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2384382046176104</v>
+        <v>0.235665667354615</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2221868972128734</v>
+        <v>0.2240868972128733</v>
       </c>
       <c r="C88">
-        <v>-51.40323808593061</v>
+        <v>-52.31781569668057</v>
       </c>
       <c r="D88">
-        <v>10.37876191406938</v>
+        <v>10.27118430331942</v>
       </c>
       <c r="E88">
-        <v>5.401999999999994</v>
+        <v>6.208999999999996</v>
       </c>
       <c r="F88">
-        <v>69.40199999999999</v>
+        <v>70.20899999999999</v>
       </c>
       <c r="G88">
         <v>7.62</v>
@@ -8616,37 +8616,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M88">
-        <v>16.3649916</v>
+        <v>16.5552822</v>
       </c>
       <c r="N88">
-        <v>-12.50832493333333</v>
+        <v>-12.69861553333333</v>
       </c>
       <c r="O88">
-        <v>-2.501664986666666</v>
+        <v>-2.539723106666666</v>
       </c>
       <c r="P88">
-        <v>-10.00665994666666</v>
+        <v>-10.15889242666666</v>
       </c>
       <c r="Q88">
-        <v>-9.946659946666662</v>
+        <v>-10.09889242666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2068352220226776</v>
+        <v>0.2192225467936528</v>
       </c>
       <c r="T88">
-        <v>3.054778655574186</v>
+        <v>3.289761629079893</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04713313347092299</v>
+        <v>0.04659137331608479</v>
       </c>
       <c r="W88">
-        <v>0.2246860071275564</v>
+        <v>0.2248137541720672</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.235665667354615</v>
+        <v>0.232956866580424</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2240868972128733</v>
+        <v>0.2259868972128733</v>
       </c>
       <c r="C89">
-        <v>-52.31781569668057</v>
+        <v>-53.23018606584593</v>
       </c>
       <c r="D89">
-        <v>10.27118430331942</v>
+        <v>10.16581393415406</v>
       </c>
       <c r="E89">
-        <v>6.208999999999996</v>
+        <v>7.015999999999998</v>
       </c>
       <c r="F89">
-        <v>70.20899999999999</v>
+        <v>71.01599999999999</v>
       </c>
       <c r="G89">
         <v>7.62</v>
@@ -8698,37 +8698,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M89">
-        <v>16.5552822</v>
+        <v>16.7455728</v>
       </c>
       <c r="N89">
-        <v>-12.69861553333333</v>
+        <v>-12.88890613333333</v>
       </c>
       <c r="O89">
-        <v>-2.539723106666666</v>
+        <v>-2.577781226666666</v>
       </c>
       <c r="P89">
-        <v>-10.15889242666666</v>
+        <v>-10.31112490666666</v>
       </c>
       <c r="Q89">
-        <v>-10.09889242666666</v>
+        <v>-10.25112490666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2192225467936528</v>
+        <v>0.2336744256931239</v>
       </c>
       <c r="T89">
-        <v>3.289761629079893</v>
+        <v>3.563908431503218</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04659137331608479</v>
+        <v>0.04606192589203837</v>
       </c>
       <c r="W89">
-        <v>0.2248137541720672</v>
+        <v>0.2249385978746574</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.232956866580424</v>
+        <v>0.2303096294601918</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2259868972128733</v>
+        <v>0.2278868972128733</v>
       </c>
       <c r="C90">
-        <v>-53.23018606584593</v>
+        <v>-54.14041643478028</v>
       </c>
       <c r="D90">
-        <v>10.16581393415406</v>
+        <v>10.06258356521971</v>
       </c>
       <c r="E90">
-        <v>7.015999999999998</v>
+        <v>7.823</v>
       </c>
       <c r="F90">
-        <v>71.01599999999999</v>
+        <v>71.82299999999999</v>
       </c>
       <c r="G90">
         <v>7.62</v>
@@ -8780,37 +8780,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M90">
-        <v>16.7455728</v>
+        <v>16.9358634</v>
       </c>
       <c r="N90">
-        <v>-12.88890613333333</v>
+        <v>-13.07919673333333</v>
       </c>
       <c r="O90">
-        <v>-2.577781226666666</v>
+        <v>-2.615839346666666</v>
       </c>
       <c r="P90">
-        <v>-10.31112490666666</v>
+        <v>-10.46335738666667</v>
       </c>
       <c r="Q90">
-        <v>-10.25112490666666</v>
+        <v>-10.40335738666666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2336744256931239</v>
+        <v>0.2507539189379533</v>
       </c>
       <c r="T90">
-        <v>3.563908431503218</v>
+        <v>3.88790010709442</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04606192589203837</v>
+        <v>0.04554437616291435</v>
       </c>
       <c r="W90">
-        <v>0.2249385978746574</v>
+        <v>0.2250606361007848</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2303096294601918</v>
+        <v>0.2277218808145718</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2278868972128733</v>
+        <v>0.2297868972128733</v>
       </c>
       <c r="C91">
-        <v>-54.14041643478028</v>
+        <v>-55.04857134104143</v>
       </c>
       <c r="D91">
-        <v>10.06258356521971</v>
+        <v>9.961428658958566</v>
       </c>
       <c r="E91">
-        <v>7.823</v>
+        <v>8.630000000000003</v>
       </c>
       <c r="F91">
-        <v>71.82299999999999</v>
+        <v>72.63</v>
       </c>
       <c r="G91">
         <v>7.62</v>
@@ -8862,37 +8862,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M91">
-        <v>16.9358634</v>
+        <v>17.126154</v>
       </c>
       <c r="N91">
-        <v>-13.07919673333333</v>
+        <v>-13.26948733333333</v>
       </c>
       <c r="O91">
-        <v>-2.615839346666666</v>
+        <v>-2.653897466666667</v>
       </c>
       <c r="P91">
-        <v>-10.46335738666667</v>
+        <v>-10.61558986666667</v>
       </c>
       <c r="Q91">
-        <v>-10.40335738666666</v>
+        <v>-10.55558986666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2507539189379533</v>
+        <v>0.2712493108317487</v>
       </c>
       <c r="T91">
-        <v>3.88790010709442</v>
+        <v>4.276690117803863</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04554437616291435</v>
+        <v>0.04503832753888196</v>
       </c>
       <c r="W91">
-        <v>0.2250606361007848</v>
+        <v>0.2251799623663316</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2277218808145718</v>
+        <v>0.2251916376944099</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2297868972128733</v>
+        <v>0.2316868972128734</v>
       </c>
       <c r="C92">
-        <v>-55.04857134104143</v>
+        <v>-55.95471275293937</v>
       </c>
       <c r="D92">
-        <v>9.961428658958566</v>
+        <v>9.86228724706063</v>
       </c>
       <c r="E92">
-        <v>8.630000000000003</v>
+        <v>9.437000000000005</v>
       </c>
       <c r="F92">
-        <v>72.63</v>
+        <v>73.437</v>
       </c>
       <c r="G92">
         <v>7.62</v>
@@ -8944,37 +8944,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M92">
-        <v>17.126154</v>
+        <v>17.3164446</v>
       </c>
       <c r="N92">
-        <v>-13.26948733333333</v>
+        <v>-13.45977793333333</v>
       </c>
       <c r="O92">
-        <v>-2.653897466666667</v>
+        <v>-2.691955586666667</v>
       </c>
       <c r="P92">
-        <v>-10.61558986666667</v>
+        <v>-10.76782234666667</v>
       </c>
       <c r="Q92">
-        <v>-10.55558986666666</v>
+        <v>-10.70782234666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2712493108317487</v>
+        <v>0.2962992342574986</v>
       </c>
       <c r="T92">
-        <v>4.276690117803863</v>
+        <v>4.751877908670958</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04503832753888196</v>
+        <v>0.04454340086263051</v>
       </c>
       <c r="W92">
-        <v>0.2251799623663316</v>
+        <v>0.2252966660765917</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2251916376944099</v>
+        <v>0.2227170043131526</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2316868972128734</v>
+        <v>0.2335868972128734</v>
       </c>
       <c r="C93">
-        <v>-55.95471275293937</v>
+        <v>-56.85890019612901</v>
       </c>
       <c r="D93">
-        <v>9.86228724706063</v>
+        <v>9.765099803870994</v>
       </c>
       <c r="E93">
-        <v>9.437000000000005</v>
+        <v>10.24400000000001</v>
       </c>
       <c r="F93">
-        <v>73.437</v>
+        <v>74.244</v>
       </c>
       <c r="G93">
         <v>7.62</v>
@@ -9026,37 +9026,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M93">
-        <v>17.3164446</v>
+        <v>17.5067352</v>
       </c>
       <c r="N93">
-        <v>-13.45977793333333</v>
+        <v>-13.65006853333333</v>
       </c>
       <c r="O93">
-        <v>-2.691955586666667</v>
+        <v>-2.730013706666667</v>
       </c>
       <c r="P93">
-        <v>-10.76782234666667</v>
+        <v>-10.92005482666667</v>
       </c>
       <c r="Q93">
-        <v>-10.70782234666667</v>
+        <v>-10.86005482666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2962992342574986</v>
+        <v>0.327611638539686</v>
       </c>
       <c r="T93">
-        <v>4.751877908670958</v>
+        <v>5.34586264725483</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04454340086263051</v>
+        <v>0.04405923346194974</v>
       </c>
       <c r="W93">
-        <v>0.2252966660765917</v>
+        <v>0.2254108327496723</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2227170043131526</v>
+        <v>0.2202961673097487</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2335868972128734</v>
+        <v>0.2354868972128734</v>
       </c>
       <c r="C94">
-        <v>-56.85890019612901</v>
+        <v>-57.76119087279077</v>
       </c>
       <c r="D94">
-        <v>9.765099803870994</v>
+        <v>9.669809127209216</v>
       </c>
       <c r="E94">
-        <v>10.24400000000001</v>
+        <v>11.05099999999999</v>
       </c>
       <c r="F94">
-        <v>74.244</v>
+        <v>75.05099999999999</v>
       </c>
       <c r="G94">
         <v>7.62</v>
@@ -9108,37 +9108,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M94">
-        <v>17.5067352</v>
+        <v>17.6970258</v>
       </c>
       <c r="N94">
-        <v>-13.65006853333333</v>
+        <v>-13.84035913333333</v>
       </c>
       <c r="O94">
-        <v>-2.730013706666667</v>
+        <v>-2.768071826666667</v>
       </c>
       <c r="P94">
-        <v>-10.92005482666667</v>
+        <v>-11.07228730666666</v>
       </c>
       <c r="Q94">
-        <v>-10.86005482666667</v>
+        <v>-11.01228730666666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.327611638539686</v>
+        <v>0.3678704440453555</v>
       </c>
       <c r="T94">
-        <v>5.34586264725483</v>
+        <v>6.109557311148378</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04405923346194974</v>
+        <v>0.04358547826343416</v>
       </c>
       <c r="W94">
-        <v>0.2254108327496723</v>
+        <v>0.2255225442254822</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2202961673097487</v>
+        <v>0.2179273913171708</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2354868972128734</v>
+        <v>0.2373868972128734</v>
       </c>
       <c r="C95">
-        <v>-57.76119087279077</v>
+        <v>-58.66163977390084</v>
       </c>
       <c r="D95">
-        <v>9.669809127209216</v>
+        <v>9.576360226099144</v>
       </c>
       <c r="E95">
-        <v>11.05099999999999</v>
+        <v>11.858</v>
       </c>
       <c r="F95">
-        <v>75.05099999999999</v>
+        <v>75.85799999999999</v>
       </c>
       <c r="G95">
         <v>7.62</v>
@@ -9190,37 +9190,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M95">
-        <v>17.6970258</v>
+        <v>17.8873164</v>
       </c>
       <c r="N95">
-        <v>-13.84035913333333</v>
+        <v>-14.03064973333333</v>
       </c>
       <c r="O95">
-        <v>-2.768071826666667</v>
+        <v>-2.806129946666667</v>
       </c>
       <c r="P95">
-        <v>-11.07228730666666</v>
+        <v>-11.22451978666667</v>
       </c>
       <c r="Q95">
-        <v>-11.01228730666666</v>
+        <v>-11.16451978666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3678704440453555</v>
+        <v>0.4215488513862481</v>
       </c>
       <c r="T95">
-        <v>6.109557311148378</v>
+        <v>7.127816863006442</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04358547826343416</v>
+        <v>0.04312180296275932</v>
       </c>
       <c r="W95">
-        <v>0.2255225442254822</v>
+        <v>0.2256318788613814</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2179273913171708</v>
+        <v>0.2156090148137967</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2373868972128734</v>
+        <v>0.2392868972128734</v>
       </c>
       <c r="C96">
-        <v>-58.66163977390084</v>
+        <v>-59.56029978505362</v>
       </c>
       <c r="D96">
-        <v>9.576360226099144</v>
+        <v>9.484700214946381</v>
       </c>
       <c r="E96">
-        <v>11.858</v>
+        <v>12.665</v>
       </c>
       <c r="F96">
-        <v>75.85799999999999</v>
+        <v>76.66499999999999</v>
       </c>
       <c r="G96">
         <v>7.62</v>
@@ -9272,37 +9272,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M96">
-        <v>17.8873164</v>
+        <v>18.077607</v>
       </c>
       <c r="N96">
-        <v>-14.03064973333333</v>
+        <v>-14.22094033333333</v>
       </c>
       <c r="O96">
-        <v>-2.806129946666667</v>
+        <v>-2.844188066666667</v>
       </c>
       <c r="P96">
-        <v>-11.22451978666667</v>
+        <v>-11.37675226666667</v>
       </c>
       <c r="Q96">
-        <v>-11.16451978666666</v>
+        <v>-11.31675226666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4215488513862481</v>
+        <v>0.496698621663498</v>
       </c>
       <c r="T96">
-        <v>7.127816863006442</v>
+        <v>8.553380235607735</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04312180296275932</v>
+        <v>0.04266788924736185</v>
       </c>
       <c r="W96">
-        <v>0.2256318788613814</v>
+        <v>0.2257389117154721</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2156090148137967</v>
+        <v>0.2133394462368093</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2392868972128734</v>
+        <v>0.2411868972128734</v>
       </c>
       <c r="C97">
-        <v>-59.56029978505362</v>
+        <v>-60.45722178626467</v>
       </c>
       <c r="D97">
-        <v>9.484700214946381</v>
+        <v>9.394778213735327</v>
       </c>
       <c r="E97">
-        <v>12.665</v>
+        <v>13.472</v>
       </c>
       <c r="F97">
-        <v>76.66499999999999</v>
+        <v>77.47199999999999</v>
       </c>
       <c r="G97">
         <v>7.62</v>
@@ -9354,37 +9354,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M97">
-        <v>18.077607</v>
+        <v>18.2678976</v>
       </c>
       <c r="N97">
-        <v>-14.22094033333333</v>
+        <v>-14.41123093333333</v>
       </c>
       <c r="O97">
-        <v>-2.844188066666667</v>
+        <v>-2.882246186666666</v>
       </c>
       <c r="P97">
-        <v>-11.37675226666667</v>
+        <v>-11.52898474666666</v>
       </c>
       <c r="Q97">
-        <v>-11.31675226666667</v>
+        <v>-11.46898474666666</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.496698621663498</v>
+        <v>0.6094232770793727</v>
       </c>
       <c r="T97">
-        <v>8.553380235607735</v>
+        <v>10.69172529450967</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04266788924736185</v>
+        <v>0.04222343206770184</v>
       </c>
       <c r="W97">
-        <v>0.2257389117154721</v>
+        <v>0.2258437147184359</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2133394462368093</v>
+        <v>0.2111171603385092</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2411868972128733</v>
+        <v>0.2430868972128734</v>
       </c>
       <c r="C98">
-        <v>-60.45722178626466</v>
+        <v>-61.35245474614976</v>
       </c>
       <c r="D98">
-        <v>9.394778213735318</v>
+        <v>9.306545253850222</v>
       </c>
       <c r="E98">
-        <v>13.47199999999999</v>
+        <v>14.27899999999999</v>
       </c>
       <c r="F98">
-        <v>77.47199999999998</v>
+        <v>78.27899999999998</v>
       </c>
       <c r="G98">
         <v>7.62</v>
@@ -9436,37 +9436,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M98">
-        <v>18.2678976</v>
+        <v>18.4581882</v>
       </c>
       <c r="N98">
-        <v>-14.41123093333333</v>
+        <v>-14.60152153333333</v>
       </c>
       <c r="O98">
-        <v>-2.882246186666666</v>
+        <v>-2.920304306666666</v>
       </c>
       <c r="P98">
-        <v>-11.52898474666666</v>
+        <v>-11.68121722666666</v>
       </c>
       <c r="Q98">
-        <v>-11.46898474666666</v>
+        <v>-11.62121722666666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6094232770793711</v>
+        <v>0.797297702772495</v>
       </c>
       <c r="T98">
-        <v>10.69172529450964</v>
+        <v>14.25563372601286</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04222343206770184</v>
+        <v>0.04178813895360183</v>
       </c>
       <c r="W98">
-        <v>0.2258437147184359</v>
+        <v>0.2259463568347407</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2111171603385092</v>
+        <v>0.2089406947680091</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2430868972128734</v>
+        <v>0.2449868972128733</v>
       </c>
       <c r="C99">
-        <v>-61.35245474614976</v>
+        <v>-62.24604581084616</v>
       </c>
       <c r="D99">
-        <v>9.306545253850222</v>
+        <v>9.219954189153828</v>
       </c>
       <c r="E99">
-        <v>14.27899999999999</v>
+        <v>15.08599999999999</v>
       </c>
       <c r="F99">
-        <v>78.27899999999998</v>
+        <v>79.08599999999998</v>
       </c>
       <c r="G99">
         <v>7.62</v>
@@ -9518,37 +9518,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M99">
-        <v>18.4581882</v>
+        <v>18.6484788</v>
       </c>
       <c r="N99">
-        <v>-14.60152153333333</v>
+        <v>-14.79181213333333</v>
       </c>
       <c r="O99">
-        <v>-2.920304306666666</v>
+        <v>-2.958362426666666</v>
       </c>
       <c r="P99">
-        <v>-11.68121722666666</v>
+        <v>-11.83344970666666</v>
       </c>
       <c r="Q99">
-        <v>-11.62121722666666</v>
+        <v>-11.77344970666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.797297702772495</v>
+        <v>1.173046554158742</v>
       </c>
       <c r="T99">
-        <v>14.25563372601286</v>
+        <v>21.38345058901929</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04178813895360183</v>
+        <v>0.04136172937244263</v>
       </c>
       <c r="W99">
-        <v>0.2259463568347407</v>
+        <v>0.226046904213978</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2089406947680091</v>
+        <v>0.2068086468622131</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2449868972128733</v>
+        <v>0.2468868972128734</v>
       </c>
       <c r="C100">
-        <v>-62.24604581084616</v>
+        <v>-63.13804038801572</v>
       </c>
       <c r="D100">
-        <v>9.219954189153828</v>
+        <v>9.134959611984257</v>
       </c>
       <c r="E100">
-        <v>15.08599999999999</v>
+        <v>15.89299999999999</v>
       </c>
       <c r="F100">
-        <v>79.08599999999998</v>
+        <v>79.89299999999999</v>
       </c>
       <c r="G100">
         <v>7.62</v>
@@ -9600,37 +9600,37 @@
         <v>3.856666666666667</v>
       </c>
       <c r="M100">
-        <v>18.6484788</v>
+        <v>18.8387694</v>
       </c>
       <c r="N100">
-        <v>-14.79181213333333</v>
+        <v>-14.98210273333333</v>
       </c>
       <c r="O100">
-        <v>-2.958362426666666</v>
+        <v>-2.996420546666666</v>
       </c>
       <c r="P100">
-        <v>-11.83344970666666</v>
+        <v>-11.98568218666666</v>
       </c>
       <c r="Q100">
-        <v>-11.77344970666666</v>
+        <v>-11.92568218666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.173046554158742</v>
+        <v>2.300293108317484</v>
       </c>
       <c r="T100">
-        <v>21.38345058901929</v>
+        <v>42.76690117803857</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04136172937244263</v>
+        <v>0.04094393412625633</v>
       </c>
       <c r="W100">
-        <v>0.226046904213978</v>
+        <v>0.2261454203330288</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2068086468622131</v>
+        <v>0.2047196706312817</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2468868972128734</v>
-      </c>
-      <c r="C101">
-        <v>-63.13804038801572</v>
-      </c>
-      <c r="D101">
-        <v>9.134959611984257</v>
-      </c>
-      <c r="E101">
-        <v>15.89299999999999</v>
-      </c>
-      <c r="F101">
-        <v>79.89299999999999</v>
-      </c>
-      <c r="G101">
-        <v>7.62</v>
-      </c>
-      <c r="H101">
-        <v>16.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.916666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.06000000000000005</v>
-      </c>
-      <c r="L101">
-        <v>3.856666666666667</v>
-      </c>
-      <c r="M101">
-        <v>18.8387694</v>
-      </c>
-      <c r="N101">
-        <v>-14.98210273333333</v>
-      </c>
-      <c r="O101">
-        <v>-2.996420546666666</v>
-      </c>
-      <c r="P101">
-        <v>-11.98568218666666</v>
-      </c>
-      <c r="Q101">
-        <v>-11.92568218666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.300293108317484</v>
-      </c>
-      <c r="T101">
-        <v>42.76690117803857</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04094393412625633</v>
-      </c>
-      <c r="W101">
-        <v>0.2261454203330288</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2047196706312817</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
